--- a/充填機投資回収_白鳥惣菜_48期.xlsx
+++ b/充填機投資回収_白鳥惣菜_48期.xlsx
@@ -1233,7 +1233,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">・電気工事費は見積未定のため</t>
+      <t xml:space="preserve">・電気工事費</t>
     </r>
     <r>
       <rPr>
@@ -1243,7 +1243,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0</t>
+      <t xml:space="preserve">50</t>
     </r>
     <r>
       <rPr>
@@ -1252,7 +1252,45 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">円で試算。金額と会計処理区分を「前提条件」下部に入力すると全シートに反映されます。</t>
+      <t xml:space="preserve">万円は機械の付随費用として取得価額に含め、機械と同じ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年で償却（区分</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。変更は「前提条件」下部で入力すると全シートに反映されます。</t>
     </r>
   </si>
   <si>
@@ -3427,7 +3465,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">見積が出たら入力。</t>
+      <t xml:space="preserve">指示値：</t>
     </r>
     <r>
       <rPr>
@@ -3437,7 +3475,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0</t>
+      <t xml:space="preserve">50</t>
     </r>
     <r>
       <rPr>
@@ -3446,7 +3484,45 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">円なら全シートで影響なし</t>
+      <t xml:space="preserve">万円（区分</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円にすると全シートで影響なし</t>
     </r>
   </si>
   <si>
@@ -7351,19 +7427,19 @@
                   <c:v>-2319.89610000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-2452.67370000001</c:v>
+                  <c:v>-2456.84036666667</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3584.25429999997</c:v>
+                  <c:v>3580.08763333334</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3864.5183</c:v>
+                  <c:v>3860.35163333331</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2540.15429999999</c:v>
+                  <c:v>2535.98763333331</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-3598.21309999999</c:v>
+                  <c:v>-3602.37976666668</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7371,11 +7447,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="4169582"/>
-        <c:axId val="50649656"/>
+        <c:axId val="58409866"/>
+        <c:axId val="84522642"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="4169582"/>
+        <c:axId val="58409866"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7407,7 +7483,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50649656"/>
+        <c:crossAx val="84522642"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7415,7 +7491,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="50649656"/>
+        <c:axId val="84522642"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7457,7 +7533,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4169582"/>
+        <c:crossAx val="58409866"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8233,184 +8309,184 @@
                 <c:formatCode>#,##0;[RED]\▲#,##0;\-</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>112808</c:v>
+                  <c:v>108641.333333333</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>242524</c:v>
+                  <c:v>234190.666666667</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>366604</c:v>
+                  <c:v>354104</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>496320</c:v>
+                  <c:v>479653.333333333</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>620400</c:v>
+                  <c:v>599566.666666667</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>750116</c:v>
+                  <c:v>725116</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>879832</c:v>
+                  <c:v>850665.333333333</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1003912</c:v>
+                  <c:v>970578.666666667</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1133628</c:v>
+                  <c:v>1096128</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1257708</c:v>
+                  <c:v>1216041.33333333</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1387424</c:v>
+                  <c:v>1341590.66666667</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1517140</c:v>
+                  <c:v>1467140</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1635584</c:v>
+                  <c:v>1581417.33333333</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1765300</c:v>
+                  <c:v>1706966.66666667</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1889380</c:v>
+                  <c:v>1826880</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2019096</c:v>
+                  <c:v>1952429.33333333</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2143176</c:v>
+                  <c:v>2072342.66666667</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2272892</c:v>
+                  <c:v>2197892</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2402608</c:v>
+                  <c:v>2323441.33333333</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2526688</c:v>
+                  <c:v>2443354.66666667</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2656404</c:v>
+                  <c:v>2568904</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2780484</c:v>
+                  <c:v>2688817.33333333</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2910200</c:v>
+                  <c:v>2814366.66666667</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>3039916</c:v>
+                  <c:v>2939916</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>3152724</c:v>
+                  <c:v>3048557.33333333</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>3282440</c:v>
+                  <c:v>3174106.66666667</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>3406520</c:v>
+                  <c:v>3294020</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>3536236</c:v>
+                  <c:v>3419569.33333333</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>3660316</c:v>
+                  <c:v>3539482.66666667</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>3790032</c:v>
+                  <c:v>3665032</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>3919748</c:v>
+                  <c:v>3790581.33333334</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>4043828</c:v>
+                  <c:v>3910494.66666667</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>4173544</c:v>
+                  <c:v>4036044</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>4297624</c:v>
+                  <c:v>4155957.33333334</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>4427340</c:v>
+                  <c:v>4281506.66666667</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>4557056</c:v>
+                  <c:v>4407056</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>4669864</c:v>
+                  <c:v>4515697.33333334</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>4799580</c:v>
+                  <c:v>4641246.66666667</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>4923660</c:v>
+                  <c:v>4761160</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>5053376</c:v>
+                  <c:v>4886709.33333333</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>5177456</c:v>
+                  <c:v>5006622.66666667</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>5307172</c:v>
+                  <c:v>5132172</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>5436888</c:v>
+                  <c:v>5257721.33333333</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>5560968</c:v>
+                  <c:v>5377634.66666667</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>5690684</c:v>
+                  <c:v>5503184</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>5814764</c:v>
+                  <c:v>5623097.33333333</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>5944480</c:v>
+                  <c:v>5748646.66666667</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>6074196</c:v>
+                  <c:v>5874196</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>6187004</c:v>
+                  <c:v>5982837.33333333</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>6316720</c:v>
+                  <c:v>6108386.66666666</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>6440800</c:v>
+                  <c:v>6228300</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>6570516</c:v>
+                  <c:v>6353849.33333333</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>6694596</c:v>
+                  <c:v>6473762.66666666</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>6824312</c:v>
+                  <c:v>6599312</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>6954028</c:v>
+                  <c:v>6724861.33333333</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>7078108</c:v>
+                  <c:v>6844774.66666666</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>7207824</c:v>
+                  <c:v>6970324</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>7331904</c:v>
+                  <c:v>7090237.33333333</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>7461620</c:v>
+                  <c:v>7215786.66666666</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>7591336</c:v>
+                  <c:v>7341335.99999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8425,11 +8501,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="24169666"/>
-        <c:axId val="80212943"/>
+        <c:axId val="10333832"/>
+        <c:axId val="86980223"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="24169666"/>
+        <c:axId val="10333832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8495,7 +8571,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80212943"/>
+        <c:crossAx val="86980223"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8503,7 +8579,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="80212943"/>
+        <c:axId val="86980223"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8579,7 +8655,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24169666"/>
+        <c:crossAx val="10333832"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9038,37 +9114,37 @@
                 <c:formatCode>#,##0;[RED]\▲#,##0;\-</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>20833.3333333333</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>29166.6666666667</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9209,11 +9285,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="72473300"/>
-        <c:axId val="17895266"/>
+        <c:axId val="63623514"/>
+        <c:axId val="92126230"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="72473300"/>
+        <c:axId val="63623514"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9245,7 +9321,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17895266"/>
+        <c:crossAx val="92126230"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9253,7 +9329,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="17895266"/>
+        <c:axId val="92126230"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9295,7 +9371,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72473300"/>
+        <c:crossAx val="63623514"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9650,19 +9726,19 @@
                   <c:v>-2319.89610000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-2452.67370000001</c:v>
+                  <c:v>-2456.84036666667</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3584.25429999997</c:v>
+                  <c:v>3580.08763333334</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3864.5183</c:v>
+                  <c:v>3860.35163333331</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2540.15429999999</c:v>
+                  <c:v>2535.98763333331</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-3598.21309999999</c:v>
+                  <c:v>-3602.37976666668</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9670,11 +9746,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="8455751"/>
-        <c:axId val="98508499"/>
+        <c:axId val="74049959"/>
+        <c:axId val="1273087"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="8455751"/>
+        <c:axId val="74049959"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9706,7 +9782,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98508499"/>
+        <c:crossAx val="1273087"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9714,7 +9790,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="98508499"/>
+        <c:axId val="1273087"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9756,7 +9832,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8455751"/>
+        <c:crossAx val="74049959"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10218,7 +10294,7 @@
       </c>
       <c r="C11" s="10" t="n">
         <f aca="false">前提条件!C85</f>
-        <v>0</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10236,7 +10312,7 @@
       </c>
       <c r="C13" s="7" t="n">
         <f aca="false">前提条件!C94</f>
-        <v>4500000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10269,7 +10345,7 @@
       </c>
       <c r="C17" s="13" t="n">
         <f aca="false">前提条件!C10+前提条件!C90</f>
-        <v>37500</v>
+        <v>41666.6666666667</v>
       </c>
       <c r="D17" s="14" t="s">
         <v>18</v>
@@ -10281,7 +10357,7 @@
       </c>
       <c r="C18" s="13" t="n">
         <f aca="false">前提条件!C79</f>
-        <v>126428.333333333</v>
+        <v>122261.666666667</v>
       </c>
       <c r="D18" s="14" t="s">
         <v>20</v>
@@ -10293,7 +10369,7 @@
       </c>
       <c r="C19" s="15" t="n">
         <f aca="false">投資回収_月次!D4</f>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D19" s="14"/>
     </row>
@@ -10303,7 +10379,7 @@
       </c>
       <c r="C20" s="16" t="n">
         <f aca="false">投資回収_月次!G4</f>
-        <v>47239</v>
+        <v>47331</v>
       </c>
       <c r="D20" s="14"/>
     </row>
@@ -10323,7 +10399,7 @@
       </c>
       <c r="C22" s="19" t="n">
         <f aca="false">白鳥惣菜PL_導入効果!P154*1000</f>
-        <v>620400.000000052</v>
+        <v>599566.666666709</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>25</v>
@@ -10335,7 +10411,7 @@
       </c>
       <c r="C23" s="13" t="n">
         <f aca="false">年度別_償却!I16</f>
-        <v>15188308</v>
+        <v>14688308</v>
       </c>
       <c r="D23" s="14"/>
     </row>
@@ -10345,7 +10421,7 @@
       </c>
       <c r="C24" s="20" t="n">
         <f aca="false">前提条件!C82</f>
-        <v>0.288992824973404</v>
+        <v>0.312425308957301</v>
       </c>
       <c r="D24" s="14" t="s">
         <v>28</v>
@@ -10501,27 +10577,27 @@
       </c>
       <c r="D36" s="30" t="n">
         <f aca="false">白鳥惣菜PL_導入効果!J153</f>
-        <v>-2452.67370000001</v>
+        <v>-2456.84036666667</v>
       </c>
       <c r="E36" s="30" t="n">
         <f aca="false">白鳥惣菜PL_導入効果!K153</f>
-        <v>3584.25429999997</v>
+        <v>3580.08763333334</v>
       </c>
       <c r="F36" s="30" t="n">
         <f aca="false">白鳥惣菜PL_導入効果!L153</f>
-        <v>3864.5183</v>
+        <v>3860.35163333331</v>
       </c>
       <c r="G36" s="30" t="n">
         <f aca="false">白鳥惣菜PL_導入効果!M153</f>
-        <v>2540.15429999999</v>
+        <v>2535.98763333331</v>
       </c>
       <c r="H36" s="30" t="n">
         <f aca="false">白鳥惣菜PL_導入効果!N153</f>
-        <v>-3598.21309999999</v>
+        <v>-3602.37976666668</v>
       </c>
       <c r="I36" s="30" t="n">
         <f aca="false">白鳥惣菜PL_導入効果!P153</f>
-        <v>1618.14399999994</v>
+        <v>1597.3106666666</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10534,27 +10610,27 @@
       </c>
       <c r="D37" s="31" t="n">
         <f aca="false">白鳥惣菜PL_導入効果!J154</f>
-        <v>112.808000000019</v>
+        <v>108.641333333362</v>
       </c>
       <c r="E37" s="31" t="n">
         <f aca="false">白鳥惣菜PL_導入効果!K154</f>
-        <v>129.715999999985</v>
+        <v>125.549333333357</v>
       </c>
       <c r="F37" s="31" t="n">
         <f aca="false">白鳥惣菜PL_導入効果!L154</f>
-        <v>124.080000000016</v>
+        <v>119.91333333333</v>
       </c>
       <c r="G37" s="31" t="n">
         <f aca="false">白鳥惣菜PL_導入効果!M154</f>
-        <v>129.716000000015</v>
+        <v>125.549333333329</v>
       </c>
       <c r="H37" s="31" t="n">
         <f aca="false">白鳥惣菜PL_導入効果!N154</f>
-        <v>124.080000000016</v>
+        <v>119.91333333333</v>
       </c>
       <c r="I37" s="31" t="n">
         <f aca="false">白鳥惣菜PL_導入効果!P154</f>
-        <v>620.400000000052</v>
+        <v>599.566666666709</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11067,7 +11143,7 @@
       </c>
       <c r="C13" s="46" t="n">
         <f aca="false">C94</f>
-        <v>4500000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11972,7 +12048,7 @@
       </c>
       <c r="C77" s="39" t="n">
         <f aca="false">(C10+C90)*12</f>
-        <v>450000</v>
+        <v>500000</v>
       </c>
       <c r="D77" s="42" t="s">
         <v>185</v>
@@ -11987,7 +12063,7 @@
       </c>
       <c r="C78" s="59" t="n">
         <f aca="false">C75-C77</f>
-        <v>1517140</v>
+        <v>1467140</v>
       </c>
       <c r="D78" s="42" t="s">
         <v>185</v>
@@ -12002,7 +12078,7 @@
       </c>
       <c r="C79" s="39" t="n">
         <f aca="false">C78/12</f>
-        <v>126428.333333333</v>
+        <v>122261.666666667</v>
       </c>
       <c r="D79" s="42" t="s">
         <v>93</v>
@@ -12015,7 +12091,7 @@
       </c>
       <c r="C80" s="60" t="n">
         <f aca="false">IF(C76&gt;0,C94/C76,0)</f>
-        <v>27.4510202629198</v>
+        <v>30.5011336254664</v>
       </c>
       <c r="D80" s="42" t="s">
         <v>198</v>
@@ -12030,7 +12106,7 @@
       </c>
       <c r="C81" s="58" t="n">
         <f aca="false">C80/12</f>
-        <v>2.28758502190998</v>
+        <v>2.54176113545553</v>
       </c>
       <c r="D81" s="42" t="s">
         <v>90</v>
@@ -12043,7 +12119,7 @@
       </c>
       <c r="C82" s="61" t="n">
         <f aca="false">IF((C71+C72)&gt;0,(C73+C74+C77)/(C71+C72),0)</f>
-        <v>0.288992824973404</v>
+        <v>0.312425308957301</v>
       </c>
       <c r="D82" s="2"/>
       <c r="H82" s="14" t="s">
@@ -12066,7 +12142,7 @@
         <v>203</v>
       </c>
       <c r="C85" s="38" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="D85" s="42" t="s">
         <v>82</v>
@@ -12133,7 +12209,7 @@
       </c>
       <c r="C90" s="39" t="n">
         <f aca="false">IF(C89&gt;0,C85/(C89*12),0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="D90" s="42" t="s">
         <v>93</v>
@@ -12184,7 +12260,7 @@
       </c>
       <c r="C94" s="59" t="n">
         <f aca="false">C8+C85</f>
-        <v>4500000</v>
+        <v>5000000</v>
       </c>
       <c r="D94" s="42" t="s">
         <v>82</v>
@@ -12251,14 +12327,14 @@
       </c>
       <c r="D4" s="63" t="n">
         <f aca="false">IF(MAX(K8:K127)&gt;=前提条件!$C$94,COUNTIF(K8:K127,"&lt;"&amp;前提条件!$C$94)+1,"回収不可")</f>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>22</v>
       </c>
       <c r="G4" s="64" t="n">
         <f aca="false">IF(ISNUMBER(D4),EDATE(前提条件!$C$11,D4-1),"-")</f>
-        <v>47239</v>
+        <v>47331</v>
       </c>
       <c r="I4" s="18" t="s">
         <v>223</v>
@@ -12379,7 +12455,7 @@
       </c>
       <c r="L8" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K8,0)</f>
-        <v>4349692</v>
+        <v>4849692</v>
       </c>
       <c r="M8" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -12387,15 +12463,15 @@
       </c>
       <c r="N8" s="72" t="n">
         <f aca="false">J8-M8-R8-S8</f>
-        <v>112808</v>
+        <v>108641.333333333</v>
       </c>
       <c r="O8" s="72" t="n">
         <f aca="false">N8</f>
-        <v>112808</v>
+        <v>108641.333333333</v>
       </c>
       <c r="P8" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M8)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R8),0)</f>
-        <v>4462500</v>
+        <v>4958333.33333333</v>
       </c>
       <c r="Q8" s="73" t="str">
         <f aca="false">IF(AND(K8&gt;=前提条件!$C$94,0&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -12403,7 +12479,7 @@
       </c>
       <c r="R8" s="34" t="n">
         <f aca="false">IF(A8&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S8" s="34" t="n">
         <f aca="false">IF(A8=1,前提条件!$C$91,0)</f>
@@ -12455,7 +12531,7 @@
       </c>
       <c r="L9" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K9,0)</f>
-        <v>4182476</v>
+        <v>4682476</v>
       </c>
       <c r="M9" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -12463,15 +12539,15 @@
       </c>
       <c r="N9" s="72" t="n">
         <f aca="false">J9-M9-R9-S9</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O9" s="72" t="n">
         <f aca="false">O8+N9</f>
-        <v>242524</v>
+        <v>234190.666666667</v>
       </c>
       <c r="P9" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M9)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R9),0)</f>
-        <v>4425000</v>
+        <v>4916666.66666667</v>
       </c>
       <c r="Q9" s="73" t="str">
         <f aca="false">IF(AND(K9&gt;=前提条件!$C$94,K8&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -12479,7 +12555,7 @@
       </c>
       <c r="R9" s="34" t="n">
         <f aca="false">IF(A9&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S9" s="34" t="n">
         <f aca="false">IF(A9=1,前提条件!$C$91,0)</f>
@@ -12531,7 +12607,7 @@
       </c>
       <c r="L10" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K10,0)</f>
-        <v>4020896</v>
+        <v>4520896</v>
       </c>
       <c r="M10" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -12539,15 +12615,15 @@
       </c>
       <c r="N10" s="72" t="n">
         <f aca="false">J10-M10-R10-S10</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O10" s="72" t="n">
         <f aca="false">O9+N10</f>
-        <v>366604</v>
+        <v>354104</v>
       </c>
       <c r="P10" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M10)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R10),0)</f>
-        <v>4387500</v>
+        <v>4875000</v>
       </c>
       <c r="Q10" s="73" t="str">
         <f aca="false">IF(AND(K10&gt;=前提条件!$C$94,K9&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -12555,7 +12631,7 @@
       </c>
       <c r="R10" s="34" t="n">
         <f aca="false">IF(A10&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S10" s="34" t="n">
         <f aca="false">IF(A10=1,前提条件!$C$91,0)</f>
@@ -12607,7 +12683,7 @@
       </c>
       <c r="L11" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K11,0)</f>
-        <v>3853680</v>
+        <v>4353680</v>
       </c>
       <c r="M11" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -12615,15 +12691,15 @@
       </c>
       <c r="N11" s="72" t="n">
         <f aca="false">J11-M11-R11-S11</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O11" s="72" t="n">
         <f aca="false">O10+N11</f>
-        <v>496320</v>
+        <v>479653.333333333</v>
       </c>
       <c r="P11" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M11)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R11),0)</f>
-        <v>4350000</v>
+        <v>4833333.33333333</v>
       </c>
       <c r="Q11" s="73" t="str">
         <f aca="false">IF(AND(K11&gt;=前提条件!$C$94,K10&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -12631,7 +12707,7 @@
       </c>
       <c r="R11" s="34" t="n">
         <f aca="false">IF(A11&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S11" s="34" t="n">
         <f aca="false">IF(A11=1,前提条件!$C$91,0)</f>
@@ -12683,7 +12759,7 @@
       </c>
       <c r="L12" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K12,0)</f>
-        <v>3692100</v>
+        <v>4192100</v>
       </c>
       <c r="M12" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -12691,15 +12767,15 @@
       </c>
       <c r="N12" s="72" t="n">
         <f aca="false">J12-M12-R12-S12</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O12" s="72" t="n">
         <f aca="false">O11+N12</f>
-        <v>620400</v>
+        <v>599566.666666667</v>
       </c>
       <c r="P12" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M12)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R12),0)</f>
-        <v>4312500</v>
+        <v>4791666.66666667</v>
       </c>
       <c r="Q12" s="73" t="str">
         <f aca="false">IF(AND(K12&gt;=前提条件!$C$94,K11&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -12707,7 +12783,7 @@
       </c>
       <c r="R12" s="34" t="n">
         <f aca="false">IF(A12&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S12" s="34" t="n">
         <f aca="false">IF(A12=1,前提条件!$C$91,0)</f>
@@ -12759,7 +12835,7 @@
       </c>
       <c r="L13" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K13,0)</f>
-        <v>3524884</v>
+        <v>4024884</v>
       </c>
       <c r="M13" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -12767,15 +12843,15 @@
       </c>
       <c r="N13" s="72" t="n">
         <f aca="false">J13-M13-R13-S13</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O13" s="72" t="n">
         <f aca="false">O12+N13</f>
-        <v>750116</v>
+        <v>725116</v>
       </c>
       <c r="P13" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M13)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R13),0)</f>
-        <v>4275000</v>
+        <v>4750000</v>
       </c>
       <c r="Q13" s="73" t="str">
         <f aca="false">IF(AND(K13&gt;=前提条件!$C$94,K12&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -12783,7 +12859,7 @@
       </c>
       <c r="R13" s="34" t="n">
         <f aca="false">IF(A13&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S13" s="34" t="n">
         <f aca="false">IF(A13=1,前提条件!$C$91,0)</f>
@@ -12835,7 +12911,7 @@
       </c>
       <c r="L14" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K14,0)</f>
-        <v>3357668</v>
+        <v>3857668</v>
       </c>
       <c r="M14" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -12843,15 +12919,15 @@
       </c>
       <c r="N14" s="72" t="n">
         <f aca="false">J14-M14-R14-S14</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O14" s="72" t="n">
         <f aca="false">O13+N14</f>
-        <v>879832</v>
+        <v>850665.333333333</v>
       </c>
       <c r="P14" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M14)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R14),0)</f>
-        <v>4237500</v>
+        <v>4708333.33333333</v>
       </c>
       <c r="Q14" s="73" t="str">
         <f aca="false">IF(AND(K14&gt;=前提条件!$C$94,K13&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -12859,7 +12935,7 @@
       </c>
       <c r="R14" s="34" t="n">
         <f aca="false">IF(A14&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S14" s="34" t="n">
         <f aca="false">IF(A14=1,前提条件!$C$91,0)</f>
@@ -12911,7 +12987,7 @@
       </c>
       <c r="L15" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K15,0)</f>
-        <v>3196088</v>
+        <v>3696088</v>
       </c>
       <c r="M15" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -12919,15 +12995,15 @@
       </c>
       <c r="N15" s="72" t="n">
         <f aca="false">J15-M15-R15-S15</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O15" s="72" t="n">
         <f aca="false">O14+N15</f>
-        <v>1003912</v>
+        <v>970578.666666667</v>
       </c>
       <c r="P15" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M15)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R15),0)</f>
-        <v>4200000</v>
+        <v>4666666.66666667</v>
       </c>
       <c r="Q15" s="73" t="str">
         <f aca="false">IF(AND(K15&gt;=前提条件!$C$94,K14&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -12935,7 +13011,7 @@
       </c>
       <c r="R15" s="34" t="n">
         <f aca="false">IF(A15&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S15" s="34" t="n">
         <f aca="false">IF(A15=1,前提条件!$C$91,0)</f>
@@ -12987,7 +13063,7 @@
       </c>
       <c r="L16" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K16,0)</f>
-        <v>3028872</v>
+        <v>3528872</v>
       </c>
       <c r="M16" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -12995,15 +13071,15 @@
       </c>
       <c r="N16" s="72" t="n">
         <f aca="false">J16-M16-R16-S16</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O16" s="72" t="n">
         <f aca="false">O15+N16</f>
-        <v>1133628</v>
+        <v>1096128</v>
       </c>
       <c r="P16" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M16)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R16),0)</f>
-        <v>4162500</v>
+        <v>4625000</v>
       </c>
       <c r="Q16" s="73" t="str">
         <f aca="false">IF(AND(K16&gt;=前提条件!$C$94,K15&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -13011,7 +13087,7 @@
       </c>
       <c r="R16" s="34" t="n">
         <f aca="false">IF(A16&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S16" s="34" t="n">
         <f aca="false">IF(A16=1,前提条件!$C$91,0)</f>
@@ -13063,7 +13139,7 @@
       </c>
       <c r="L17" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K17,0)</f>
-        <v>2867292</v>
+        <v>3367292</v>
       </c>
       <c r="M17" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -13071,15 +13147,15 @@
       </c>
       <c r="N17" s="72" t="n">
         <f aca="false">J17-M17-R17-S17</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O17" s="72" t="n">
         <f aca="false">O16+N17</f>
-        <v>1257708</v>
+        <v>1216041.33333333</v>
       </c>
       <c r="P17" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M17)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R17),0)</f>
-        <v>4125000</v>
+        <v>4583333.33333333</v>
       </c>
       <c r="Q17" s="73" t="str">
         <f aca="false">IF(AND(K17&gt;=前提条件!$C$94,K16&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -13087,7 +13163,7 @@
       </c>
       <c r="R17" s="34" t="n">
         <f aca="false">IF(A17&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S17" s="34" t="n">
         <f aca="false">IF(A17=1,前提条件!$C$91,0)</f>
@@ -13139,7 +13215,7 @@
       </c>
       <c r="L18" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K18,0)</f>
-        <v>2700076</v>
+        <v>3200076</v>
       </c>
       <c r="M18" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -13147,15 +13223,15 @@
       </c>
       <c r="N18" s="72" t="n">
         <f aca="false">J18-M18-R18-S18</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O18" s="72" t="n">
         <f aca="false">O17+N18</f>
-        <v>1387424</v>
+        <v>1341590.66666667</v>
       </c>
       <c r="P18" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M18)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R18),0)</f>
-        <v>4087500</v>
+        <v>4541666.66666667</v>
       </c>
       <c r="Q18" s="73" t="str">
         <f aca="false">IF(AND(K18&gt;=前提条件!$C$94,K17&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -13163,7 +13239,7 @@
       </c>
       <c r="R18" s="34" t="n">
         <f aca="false">IF(A18&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S18" s="34" t="n">
         <f aca="false">IF(A18=1,前提条件!$C$91,0)</f>
@@ -13215,7 +13291,7 @@
       </c>
       <c r="L19" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K19,0)</f>
-        <v>2532860</v>
+        <v>3032860</v>
       </c>
       <c r="M19" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -13223,15 +13299,15 @@
       </c>
       <c r="N19" s="72" t="n">
         <f aca="false">J19-M19-R19-S19</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O19" s="72" t="n">
         <f aca="false">O18+N19</f>
-        <v>1517140</v>
+        <v>1467140</v>
       </c>
       <c r="P19" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M19)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R19),0)</f>
-        <v>4050000</v>
+        <v>4500000</v>
       </c>
       <c r="Q19" s="73" t="str">
         <f aca="false">IF(AND(K19&gt;=前提条件!$C$94,K18&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -13239,7 +13315,7 @@
       </c>
       <c r="R19" s="34" t="n">
         <f aca="false">IF(A19&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S19" s="34" t="n">
         <f aca="false">IF(A19=1,前提条件!$C$91,0)</f>
@@ -13291,7 +13367,7 @@
       </c>
       <c r="L20" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K20,0)</f>
-        <v>2376916</v>
+        <v>2876916</v>
       </c>
       <c r="M20" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -13299,15 +13375,15 @@
       </c>
       <c r="N20" s="72" t="n">
         <f aca="false">J20-M20-R20-S20</f>
-        <v>118444</v>
+        <v>114277.333333333</v>
       </c>
       <c r="O20" s="72" t="n">
         <f aca="false">O19+N20</f>
-        <v>1635584</v>
+        <v>1581417.33333333</v>
       </c>
       <c r="P20" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M20)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R20),0)</f>
-        <v>4012500</v>
+        <v>4458333.33333333</v>
       </c>
       <c r="Q20" s="73" t="str">
         <f aca="false">IF(AND(K20&gt;=前提条件!$C$94,K19&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -13315,7 +13391,7 @@
       </c>
       <c r="R20" s="34" t="n">
         <f aca="false">IF(A20&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S20" s="34" t="n">
         <f aca="false">IF(A20=1,前提条件!$C$91,0)</f>
@@ -13367,7 +13443,7 @@
       </c>
       <c r="L21" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K21,0)</f>
-        <v>2209700</v>
+        <v>2709700</v>
       </c>
       <c r="M21" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -13375,15 +13451,15 @@
       </c>
       <c r="N21" s="72" t="n">
         <f aca="false">J21-M21-R21-S21</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O21" s="72" t="n">
         <f aca="false">O20+N21</f>
-        <v>1765300</v>
+        <v>1706966.66666667</v>
       </c>
       <c r="P21" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M21)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R21),0)</f>
-        <v>3975000</v>
+        <v>4416666.66666667</v>
       </c>
       <c r="Q21" s="73" t="str">
         <f aca="false">IF(AND(K21&gt;=前提条件!$C$94,K20&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -13391,7 +13467,7 @@
       </c>
       <c r="R21" s="34" t="n">
         <f aca="false">IF(A21&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S21" s="34" t="n">
         <f aca="false">IF(A21=1,前提条件!$C$91,0)</f>
@@ -13443,7 +13519,7 @@
       </c>
       <c r="L22" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K22,0)</f>
-        <v>2048120</v>
+        <v>2548120</v>
       </c>
       <c r="M22" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -13451,15 +13527,15 @@
       </c>
       <c r="N22" s="72" t="n">
         <f aca="false">J22-M22-R22-S22</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O22" s="72" t="n">
         <f aca="false">O21+N22</f>
-        <v>1889380</v>
+        <v>1826880</v>
       </c>
       <c r="P22" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M22)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R22),0)</f>
-        <v>3937500</v>
+        <v>4375000</v>
       </c>
       <c r="Q22" s="73" t="str">
         <f aca="false">IF(AND(K22&gt;=前提条件!$C$94,K21&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -13467,7 +13543,7 @@
       </c>
       <c r="R22" s="34" t="n">
         <f aca="false">IF(A22&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S22" s="34" t="n">
         <f aca="false">IF(A22=1,前提条件!$C$91,0)</f>
@@ -13519,7 +13595,7 @@
       </c>
       <c r="L23" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K23,0)</f>
-        <v>1880904</v>
+        <v>2380904</v>
       </c>
       <c r="M23" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -13527,15 +13603,15 @@
       </c>
       <c r="N23" s="72" t="n">
         <f aca="false">J23-M23-R23-S23</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O23" s="72" t="n">
         <f aca="false">O22+N23</f>
-        <v>2019096</v>
+        <v>1952429.33333333</v>
       </c>
       <c r="P23" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M23)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R23),0)</f>
-        <v>3900000</v>
+        <v>4333333.33333333</v>
       </c>
       <c r="Q23" s="73" t="str">
         <f aca="false">IF(AND(K23&gt;=前提条件!$C$94,K22&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -13543,7 +13619,7 @@
       </c>
       <c r="R23" s="34" t="n">
         <f aca="false">IF(A23&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S23" s="34" t="n">
         <f aca="false">IF(A23=1,前提条件!$C$91,0)</f>
@@ -13595,7 +13671,7 @@
       </c>
       <c r="L24" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K24,0)</f>
-        <v>1719324</v>
+        <v>2219324</v>
       </c>
       <c r="M24" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -13603,15 +13679,15 @@
       </c>
       <c r="N24" s="72" t="n">
         <f aca="false">J24-M24-R24-S24</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O24" s="72" t="n">
         <f aca="false">O23+N24</f>
-        <v>2143176</v>
+        <v>2072342.66666667</v>
       </c>
       <c r="P24" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M24)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R24),0)</f>
-        <v>3862500</v>
+        <v>4291666.66666667</v>
       </c>
       <c r="Q24" s="73" t="str">
         <f aca="false">IF(AND(K24&gt;=前提条件!$C$94,K23&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -13619,7 +13695,7 @@
       </c>
       <c r="R24" s="34" t="n">
         <f aca="false">IF(A24&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S24" s="34" t="n">
         <f aca="false">IF(A24=1,前提条件!$C$91,0)</f>
@@ -13671,7 +13747,7 @@
       </c>
       <c r="L25" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K25,0)</f>
-        <v>1552108</v>
+        <v>2052108</v>
       </c>
       <c r="M25" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -13679,15 +13755,15 @@
       </c>
       <c r="N25" s="72" t="n">
         <f aca="false">J25-M25-R25-S25</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O25" s="72" t="n">
         <f aca="false">O24+N25</f>
-        <v>2272892</v>
+        <v>2197892</v>
       </c>
       <c r="P25" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M25)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R25),0)</f>
-        <v>3825000</v>
+        <v>4250000</v>
       </c>
       <c r="Q25" s="73" t="str">
         <f aca="false">IF(AND(K25&gt;=前提条件!$C$94,K24&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -13695,7 +13771,7 @@
       </c>
       <c r="R25" s="34" t="n">
         <f aca="false">IF(A25&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S25" s="34" t="n">
         <f aca="false">IF(A25=1,前提条件!$C$91,0)</f>
@@ -13747,7 +13823,7 @@
       </c>
       <c r="L26" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K26,0)</f>
-        <v>1384892</v>
+        <v>1884892</v>
       </c>
       <c r="M26" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -13755,15 +13831,15 @@
       </c>
       <c r="N26" s="72" t="n">
         <f aca="false">J26-M26-R26-S26</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O26" s="72" t="n">
         <f aca="false">O25+N26</f>
-        <v>2402608</v>
+        <v>2323441.33333333</v>
       </c>
       <c r="P26" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M26)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R26),0)</f>
-        <v>3787500</v>
+        <v>4208333.33333333</v>
       </c>
       <c r="Q26" s="73" t="str">
         <f aca="false">IF(AND(K26&gt;=前提条件!$C$94,K25&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -13771,7 +13847,7 @@
       </c>
       <c r="R26" s="34" t="n">
         <f aca="false">IF(A26&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S26" s="34" t="n">
         <f aca="false">IF(A26=1,前提条件!$C$91,0)</f>
@@ -13823,7 +13899,7 @@
       </c>
       <c r="L27" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K27,0)</f>
-        <v>1223312</v>
+        <v>1723312</v>
       </c>
       <c r="M27" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -13831,15 +13907,15 @@
       </c>
       <c r="N27" s="72" t="n">
         <f aca="false">J27-M27-R27-S27</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O27" s="72" t="n">
         <f aca="false">O26+N27</f>
-        <v>2526688</v>
+        <v>2443354.66666667</v>
       </c>
       <c r="P27" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M27)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R27),0)</f>
-        <v>3750000</v>
+        <v>4166666.66666667</v>
       </c>
       <c r="Q27" s="73" t="str">
         <f aca="false">IF(AND(K27&gt;=前提条件!$C$94,K26&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -13847,7 +13923,7 @@
       </c>
       <c r="R27" s="34" t="n">
         <f aca="false">IF(A27&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S27" s="34" t="n">
         <f aca="false">IF(A27=1,前提条件!$C$91,0)</f>
@@ -13899,7 +13975,7 @@
       </c>
       <c r="L28" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K28,0)</f>
-        <v>1056096</v>
+        <v>1556096</v>
       </c>
       <c r="M28" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -13907,15 +13983,15 @@
       </c>
       <c r="N28" s="72" t="n">
         <f aca="false">J28-M28-R28-S28</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O28" s="72" t="n">
         <f aca="false">O27+N28</f>
-        <v>2656404</v>
+        <v>2568904</v>
       </c>
       <c r="P28" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M28)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R28),0)</f>
-        <v>3712500</v>
+        <v>4125000</v>
       </c>
       <c r="Q28" s="73" t="str">
         <f aca="false">IF(AND(K28&gt;=前提条件!$C$94,K27&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -13923,7 +13999,7 @@
       </c>
       <c r="R28" s="34" t="n">
         <f aca="false">IF(A28&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S28" s="34" t="n">
         <f aca="false">IF(A28=1,前提条件!$C$91,0)</f>
@@ -13975,7 +14051,7 @@
       </c>
       <c r="L29" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K29,0)</f>
-        <v>894516</v>
+        <v>1394516</v>
       </c>
       <c r="M29" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -13983,15 +14059,15 @@
       </c>
       <c r="N29" s="72" t="n">
         <f aca="false">J29-M29-R29-S29</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O29" s="72" t="n">
         <f aca="false">O28+N29</f>
-        <v>2780484</v>
+        <v>2688817.33333333</v>
       </c>
       <c r="P29" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M29)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R29),0)</f>
-        <v>3675000</v>
+        <v>4083333.33333333</v>
       </c>
       <c r="Q29" s="73" t="str">
         <f aca="false">IF(AND(K29&gt;=前提条件!$C$94,K28&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -13999,7 +14075,7 @@
       </c>
       <c r="R29" s="34" t="n">
         <f aca="false">IF(A29&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S29" s="34" t="n">
         <f aca="false">IF(A29=1,前提条件!$C$91,0)</f>
@@ -14051,7 +14127,7 @@
       </c>
       <c r="L30" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K30,0)</f>
-        <v>727300</v>
+        <v>1227300</v>
       </c>
       <c r="M30" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -14059,15 +14135,15 @@
       </c>
       <c r="N30" s="72" t="n">
         <f aca="false">J30-M30-R30-S30</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O30" s="72" t="n">
         <f aca="false">O29+N30</f>
-        <v>2910200</v>
+        <v>2814366.66666667</v>
       </c>
       <c r="P30" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M30)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R30),0)</f>
-        <v>3637500</v>
+        <v>4041666.66666667</v>
       </c>
       <c r="Q30" s="73" t="str">
         <f aca="false">IF(AND(K30&gt;=前提条件!$C$94,K29&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -14075,7 +14151,7 @@
       </c>
       <c r="R30" s="34" t="n">
         <f aca="false">IF(A30&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S30" s="34" t="n">
         <f aca="false">IF(A30=1,前提条件!$C$91,0)</f>
@@ -14127,7 +14203,7 @@
       </c>
       <c r="L31" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K31,0)</f>
-        <v>560084</v>
+        <v>1060084</v>
       </c>
       <c r="M31" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -14135,15 +14211,15 @@
       </c>
       <c r="N31" s="72" t="n">
         <f aca="false">J31-M31-R31-S31</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O31" s="72" t="n">
         <f aca="false">O30+N31</f>
-        <v>3039916</v>
+        <v>2939916</v>
       </c>
       <c r="P31" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M31)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R31),0)</f>
-        <v>3600000</v>
+        <v>4000000</v>
       </c>
       <c r="Q31" s="73" t="str">
         <f aca="false">IF(AND(K31&gt;=前提条件!$C$94,K30&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -14151,7 +14227,7 @@
       </c>
       <c r="R31" s="34" t="n">
         <f aca="false">IF(A31&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S31" s="34" t="n">
         <f aca="false">IF(A31=1,前提条件!$C$91,0)</f>
@@ -14203,7 +14279,7 @@
       </c>
       <c r="L32" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K32,0)</f>
-        <v>409776</v>
+        <v>909776</v>
       </c>
       <c r="M32" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -14211,15 +14287,15 @@
       </c>
       <c r="N32" s="72" t="n">
         <f aca="false">J32-M32-R32-S32</f>
-        <v>112808</v>
+        <v>108641.333333333</v>
       </c>
       <c r="O32" s="72" t="n">
         <f aca="false">O31+N32</f>
-        <v>3152724</v>
+        <v>3048557.33333333</v>
       </c>
       <c r="P32" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M32)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R32),0)</f>
-        <v>3562500</v>
+        <v>3958333.33333333</v>
       </c>
       <c r="Q32" s="73" t="str">
         <f aca="false">IF(AND(K32&gt;=前提条件!$C$94,K31&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -14227,7 +14303,7 @@
       </c>
       <c r="R32" s="34" t="n">
         <f aca="false">IF(A32&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S32" s="34" t="n">
         <f aca="false">IF(A32=1,前提条件!$C$91,0)</f>
@@ -14279,7 +14355,7 @@
       </c>
       <c r="L33" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K33,0)</f>
-        <v>242560</v>
+        <v>742560</v>
       </c>
       <c r="M33" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -14287,15 +14363,15 @@
       </c>
       <c r="N33" s="72" t="n">
         <f aca="false">J33-M33-R33-S33</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O33" s="72" t="n">
         <f aca="false">O32+N33</f>
-        <v>3282440</v>
+        <v>3174106.66666667</v>
       </c>
       <c r="P33" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M33)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R33),0)</f>
-        <v>3525000</v>
+        <v>3916666.66666667</v>
       </c>
       <c r="Q33" s="73" t="str">
         <f aca="false">IF(AND(K33&gt;=前提条件!$C$94,K32&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -14303,7 +14379,7 @@
       </c>
       <c r="R33" s="34" t="n">
         <f aca="false">IF(A33&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S33" s="34" t="n">
         <f aca="false">IF(A33=1,前提条件!$C$91,0)</f>
@@ -14355,7 +14431,7 @@
       </c>
       <c r="L34" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K34,0)</f>
-        <v>80980</v>
+        <v>580980</v>
       </c>
       <c r="M34" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -14363,15 +14439,15 @@
       </c>
       <c r="N34" s="72" t="n">
         <f aca="false">J34-M34-R34-S34</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O34" s="72" t="n">
         <f aca="false">O33+N34</f>
-        <v>3406520</v>
+        <v>3294020</v>
       </c>
       <c r="P34" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M34)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R34),0)</f>
-        <v>3487500</v>
+        <v>3875000</v>
       </c>
       <c r="Q34" s="73" t="str">
         <f aca="false">IF(AND(K34&gt;=前提条件!$C$94,K33&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -14379,7 +14455,7 @@
       </c>
       <c r="R34" s="34" t="n">
         <f aca="false">IF(A34&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S34" s="34" t="n">
         <f aca="false">IF(A34=1,前提条件!$C$91,0)</f>
@@ -14431,7 +14507,7 @@
       </c>
       <c r="L35" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K35,0)</f>
-        <v>0</v>
+        <v>413764</v>
       </c>
       <c r="M35" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -14439,23 +14515,23 @@
       </c>
       <c r="N35" s="72" t="n">
         <f aca="false">J35-M35-R35-S35</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O35" s="72" t="n">
         <f aca="false">O34+N35</f>
-        <v>3536236</v>
+        <v>3419569.33333333</v>
       </c>
       <c r="P35" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M35)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R35),0)</f>
-        <v>3450000</v>
+        <v>3833333.33333333</v>
       </c>
       <c r="Q35" s="73" t="str">
         <f aca="false">IF(AND(K35&gt;=前提条件!$C$94,K34&lt;前提条件!$C$94),"◀投資回収","")</f>
-        <v>◀投資回収</v>
+        <v/>
       </c>
       <c r="R35" s="34" t="n">
         <f aca="false">IF(A35&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S35" s="34" t="n">
         <f aca="false">IF(A35=1,前提条件!$C$91,0)</f>
@@ -14507,7 +14583,7 @@
       </c>
       <c r="L36" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K36,0)</f>
-        <v>0</v>
+        <v>252184</v>
       </c>
       <c r="M36" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -14515,15 +14591,15 @@
       </c>
       <c r="N36" s="72" t="n">
         <f aca="false">J36-M36-R36-S36</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O36" s="72" t="n">
         <f aca="false">O35+N36</f>
-        <v>3660316</v>
+        <v>3539482.66666667</v>
       </c>
       <c r="P36" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M36)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R36),0)</f>
-        <v>3412500</v>
+        <v>3791666.66666667</v>
       </c>
       <c r="Q36" s="73" t="str">
         <f aca="false">IF(AND(K36&gt;=前提条件!$C$94,K35&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -14531,7 +14607,7 @@
       </c>
       <c r="R36" s="34" t="n">
         <f aca="false">IF(A36&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S36" s="34" t="n">
         <f aca="false">IF(A36=1,前提条件!$C$91,0)</f>
@@ -14583,7 +14659,7 @@
       </c>
       <c r="L37" s="72" t="n">
         <f aca="false">MAX(前提条件!$C$94-K37,0)</f>
-        <v>0</v>
+        <v>84968</v>
       </c>
       <c r="M37" s="34" t="n">
         <f aca="false">前提条件!$C$10</f>
@@ -14591,15 +14667,15 @@
       </c>
       <c r="N37" s="72" t="n">
         <f aca="false">J37-M37-R37-S37</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O37" s="72" t="n">
         <f aca="false">O36+N37</f>
-        <v>3790032</v>
+        <v>3665032</v>
       </c>
       <c r="P37" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M37)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R37),0)</f>
-        <v>3375000</v>
+        <v>3750000</v>
       </c>
       <c r="Q37" s="73" t="str">
         <f aca="false">IF(AND(K37&gt;=前提条件!$C$94,K36&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -14607,7 +14683,7 @@
       </c>
       <c r="R37" s="34" t="n">
         <f aca="false">IF(A37&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S37" s="34" t="n">
         <f aca="false">IF(A37=1,前提条件!$C$91,0)</f>
@@ -14667,23 +14743,23 @@
       </c>
       <c r="N38" s="72" t="n">
         <f aca="false">J38-M38-R38-S38</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O38" s="72" t="n">
         <f aca="false">O37+N38</f>
-        <v>3919748</v>
+        <v>3790581.33333334</v>
       </c>
       <c r="P38" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M38)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R38),0)</f>
-        <v>3337500</v>
+        <v>3708333.33333333</v>
       </c>
       <c r="Q38" s="73" t="str">
         <f aca="false">IF(AND(K38&gt;=前提条件!$C$94,K37&lt;前提条件!$C$94),"◀投資回収","")</f>
-        <v/>
+        <v>◀投資回収</v>
       </c>
       <c r="R38" s="34" t="n">
         <f aca="false">IF(A38&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S38" s="34" t="n">
         <f aca="false">IF(A38=1,前提条件!$C$91,0)</f>
@@ -14743,15 +14819,15 @@
       </c>
       <c r="N39" s="72" t="n">
         <f aca="false">J39-M39-R39-S39</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O39" s="72" t="n">
         <f aca="false">O38+N39</f>
-        <v>4043828</v>
+        <v>3910494.66666667</v>
       </c>
       <c r="P39" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M39)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R39),0)</f>
-        <v>3300000</v>
+        <v>3666666.66666667</v>
       </c>
       <c r="Q39" s="73" t="str">
         <f aca="false">IF(AND(K39&gt;=前提条件!$C$94,K38&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -14759,7 +14835,7 @@
       </c>
       <c r="R39" s="34" t="n">
         <f aca="false">IF(A39&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S39" s="34" t="n">
         <f aca="false">IF(A39=1,前提条件!$C$91,0)</f>
@@ -14819,15 +14895,15 @@
       </c>
       <c r="N40" s="72" t="n">
         <f aca="false">J40-M40-R40-S40</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O40" s="72" t="n">
         <f aca="false">O39+N40</f>
-        <v>4173544</v>
+        <v>4036044</v>
       </c>
       <c r="P40" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M40)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R40),0)</f>
-        <v>3262500</v>
+        <v>3625000</v>
       </c>
       <c r="Q40" s="73" t="str">
         <f aca="false">IF(AND(K40&gt;=前提条件!$C$94,K39&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -14835,7 +14911,7 @@
       </c>
       <c r="R40" s="34" t="n">
         <f aca="false">IF(A40&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S40" s="34" t="n">
         <f aca="false">IF(A40=1,前提条件!$C$91,0)</f>
@@ -14895,15 +14971,15 @@
       </c>
       <c r="N41" s="72" t="n">
         <f aca="false">J41-M41-R41-S41</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O41" s="72" t="n">
         <f aca="false">O40+N41</f>
-        <v>4297624</v>
+        <v>4155957.33333334</v>
       </c>
       <c r="P41" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M41)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R41),0)</f>
-        <v>3225000</v>
+        <v>3583333.33333333</v>
       </c>
       <c r="Q41" s="73" t="str">
         <f aca="false">IF(AND(K41&gt;=前提条件!$C$94,K40&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -14911,7 +14987,7 @@
       </c>
       <c r="R41" s="34" t="n">
         <f aca="false">IF(A41&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S41" s="34" t="n">
         <f aca="false">IF(A41=1,前提条件!$C$91,0)</f>
@@ -14971,15 +15047,15 @@
       </c>
       <c r="N42" s="72" t="n">
         <f aca="false">J42-M42-R42-S42</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O42" s="72" t="n">
         <f aca="false">O41+N42</f>
-        <v>4427340</v>
+        <v>4281506.66666667</v>
       </c>
       <c r="P42" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M42)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R42),0)</f>
-        <v>3187500</v>
+        <v>3541666.66666667</v>
       </c>
       <c r="Q42" s="73" t="str">
         <f aca="false">IF(AND(K42&gt;=前提条件!$C$94,K41&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -14987,7 +15063,7 @@
       </c>
       <c r="R42" s="34" t="n">
         <f aca="false">IF(A42&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S42" s="34" t="n">
         <f aca="false">IF(A42=1,前提条件!$C$91,0)</f>
@@ -15047,15 +15123,15 @@
       </c>
       <c r="N43" s="72" t="n">
         <f aca="false">J43-M43-R43-S43</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O43" s="72" t="n">
         <f aca="false">O42+N43</f>
-        <v>4557056</v>
+        <v>4407056</v>
       </c>
       <c r="P43" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M43)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R43),0)</f>
-        <v>3150000</v>
+        <v>3500000</v>
       </c>
       <c r="Q43" s="73" t="str">
         <f aca="false">IF(AND(K43&gt;=前提条件!$C$94,K42&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -15063,7 +15139,7 @@
       </c>
       <c r="R43" s="34" t="n">
         <f aca="false">IF(A43&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S43" s="34" t="n">
         <f aca="false">IF(A43=1,前提条件!$C$91,0)</f>
@@ -15123,15 +15199,15 @@
       </c>
       <c r="N44" s="72" t="n">
         <f aca="false">J44-M44-R44-S44</f>
-        <v>112808</v>
+        <v>108641.333333333</v>
       </c>
       <c r="O44" s="72" t="n">
         <f aca="false">O43+N44</f>
-        <v>4669864</v>
+        <v>4515697.33333334</v>
       </c>
       <c r="P44" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M44)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R44),0)</f>
-        <v>3112500</v>
+        <v>3458333.33333333</v>
       </c>
       <c r="Q44" s="73" t="str">
         <f aca="false">IF(AND(K44&gt;=前提条件!$C$94,K43&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -15139,7 +15215,7 @@
       </c>
       <c r="R44" s="34" t="n">
         <f aca="false">IF(A44&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S44" s="34" t="n">
         <f aca="false">IF(A44=1,前提条件!$C$91,0)</f>
@@ -15199,15 +15275,15 @@
       </c>
       <c r="N45" s="72" t="n">
         <f aca="false">J45-M45-R45-S45</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O45" s="72" t="n">
         <f aca="false">O44+N45</f>
-        <v>4799580</v>
+        <v>4641246.66666667</v>
       </c>
       <c r="P45" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M45)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R45),0)</f>
-        <v>3075000</v>
+        <v>3416666.66666667</v>
       </c>
       <c r="Q45" s="73" t="str">
         <f aca="false">IF(AND(K45&gt;=前提条件!$C$94,K44&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -15215,7 +15291,7 @@
       </c>
       <c r="R45" s="34" t="n">
         <f aca="false">IF(A45&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S45" s="34" t="n">
         <f aca="false">IF(A45=1,前提条件!$C$91,0)</f>
@@ -15275,15 +15351,15 @@
       </c>
       <c r="N46" s="72" t="n">
         <f aca="false">J46-M46-R46-S46</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O46" s="72" t="n">
         <f aca="false">O45+N46</f>
-        <v>4923660</v>
+        <v>4761160</v>
       </c>
       <c r="P46" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M46)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R46),0)</f>
-        <v>3037500</v>
+        <v>3375000</v>
       </c>
       <c r="Q46" s="73" t="str">
         <f aca="false">IF(AND(K46&gt;=前提条件!$C$94,K45&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -15291,7 +15367,7 @@
       </c>
       <c r="R46" s="34" t="n">
         <f aca="false">IF(A46&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S46" s="34" t="n">
         <f aca="false">IF(A46=1,前提条件!$C$91,0)</f>
@@ -15351,15 +15427,15 @@
       </c>
       <c r="N47" s="72" t="n">
         <f aca="false">J47-M47-R47-S47</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O47" s="72" t="n">
         <f aca="false">O46+N47</f>
-        <v>5053376</v>
+        <v>4886709.33333333</v>
       </c>
       <c r="P47" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M47)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R47),0)</f>
-        <v>3000000</v>
+        <v>3333333.33333333</v>
       </c>
       <c r="Q47" s="73" t="str">
         <f aca="false">IF(AND(K47&gt;=前提条件!$C$94,K46&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -15367,7 +15443,7 @@
       </c>
       <c r="R47" s="34" t="n">
         <f aca="false">IF(A47&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S47" s="34" t="n">
         <f aca="false">IF(A47=1,前提条件!$C$91,0)</f>
@@ -15427,15 +15503,15 @@
       </c>
       <c r="N48" s="72" t="n">
         <f aca="false">J48-M48-R48-S48</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O48" s="72" t="n">
         <f aca="false">O47+N48</f>
-        <v>5177456</v>
+        <v>5006622.66666667</v>
       </c>
       <c r="P48" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M48)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R48),0)</f>
-        <v>2962500</v>
+        <v>3291666.66666667</v>
       </c>
       <c r="Q48" s="73" t="str">
         <f aca="false">IF(AND(K48&gt;=前提条件!$C$94,K47&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -15443,7 +15519,7 @@
       </c>
       <c r="R48" s="34" t="n">
         <f aca="false">IF(A48&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S48" s="34" t="n">
         <f aca="false">IF(A48=1,前提条件!$C$91,0)</f>
@@ -15503,15 +15579,15 @@
       </c>
       <c r="N49" s="72" t="n">
         <f aca="false">J49-M49-R49-S49</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O49" s="72" t="n">
         <f aca="false">O48+N49</f>
-        <v>5307172</v>
+        <v>5132172</v>
       </c>
       <c r="P49" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M49)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R49),0)</f>
-        <v>2925000</v>
+        <v>3250000</v>
       </c>
       <c r="Q49" s="73" t="str">
         <f aca="false">IF(AND(K49&gt;=前提条件!$C$94,K48&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -15519,7 +15595,7 @@
       </c>
       <c r="R49" s="34" t="n">
         <f aca="false">IF(A49&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S49" s="34" t="n">
         <f aca="false">IF(A49=1,前提条件!$C$91,0)</f>
@@ -15579,15 +15655,15 @@
       </c>
       <c r="N50" s="72" t="n">
         <f aca="false">J50-M50-R50-S50</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O50" s="72" t="n">
         <f aca="false">O49+N50</f>
-        <v>5436888</v>
+        <v>5257721.33333333</v>
       </c>
       <c r="P50" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M50)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R50),0)</f>
-        <v>2887500</v>
+        <v>3208333.33333333</v>
       </c>
       <c r="Q50" s="73" t="str">
         <f aca="false">IF(AND(K50&gt;=前提条件!$C$94,K49&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -15595,7 +15671,7 @@
       </c>
       <c r="R50" s="34" t="n">
         <f aca="false">IF(A50&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S50" s="34" t="n">
         <f aca="false">IF(A50=1,前提条件!$C$91,0)</f>
@@ -15655,15 +15731,15 @@
       </c>
       <c r="N51" s="72" t="n">
         <f aca="false">J51-M51-R51-S51</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O51" s="72" t="n">
         <f aca="false">O50+N51</f>
-        <v>5560968</v>
+        <v>5377634.66666667</v>
       </c>
       <c r="P51" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M51)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R51),0)</f>
-        <v>2850000</v>
+        <v>3166666.66666667</v>
       </c>
       <c r="Q51" s="73" t="str">
         <f aca="false">IF(AND(K51&gt;=前提条件!$C$94,K50&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -15671,7 +15747,7 @@
       </c>
       <c r="R51" s="34" t="n">
         <f aca="false">IF(A51&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S51" s="34" t="n">
         <f aca="false">IF(A51=1,前提条件!$C$91,0)</f>
@@ -15731,15 +15807,15 @@
       </c>
       <c r="N52" s="72" t="n">
         <f aca="false">J52-M52-R52-S52</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O52" s="72" t="n">
         <f aca="false">O51+N52</f>
-        <v>5690684</v>
+        <v>5503184</v>
       </c>
       <c r="P52" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M52)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R52),0)</f>
-        <v>2812500</v>
+        <v>3125000</v>
       </c>
       <c r="Q52" s="73" t="str">
         <f aca="false">IF(AND(K52&gt;=前提条件!$C$94,K51&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -15747,7 +15823,7 @@
       </c>
       <c r="R52" s="34" t="n">
         <f aca="false">IF(A52&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S52" s="34" t="n">
         <f aca="false">IF(A52=1,前提条件!$C$91,0)</f>
@@ -15807,15 +15883,15 @@
       </c>
       <c r="N53" s="72" t="n">
         <f aca="false">J53-M53-R53-S53</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O53" s="72" t="n">
         <f aca="false">O52+N53</f>
-        <v>5814764</v>
+        <v>5623097.33333333</v>
       </c>
       <c r="P53" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M53)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R53),0)</f>
-        <v>2775000</v>
+        <v>3083333.33333333</v>
       </c>
       <c r="Q53" s="73" t="str">
         <f aca="false">IF(AND(K53&gt;=前提条件!$C$94,K52&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -15823,7 +15899,7 @@
       </c>
       <c r="R53" s="34" t="n">
         <f aca="false">IF(A53&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S53" s="34" t="n">
         <f aca="false">IF(A53=1,前提条件!$C$91,0)</f>
@@ -15883,15 +15959,15 @@
       </c>
       <c r="N54" s="72" t="n">
         <f aca="false">J54-M54-R54-S54</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O54" s="72" t="n">
         <f aca="false">O53+N54</f>
-        <v>5944480</v>
+        <v>5748646.66666667</v>
       </c>
       <c r="P54" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M54)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R54),0)</f>
-        <v>2737500</v>
+        <v>3041666.66666667</v>
       </c>
       <c r="Q54" s="73" t="str">
         <f aca="false">IF(AND(K54&gt;=前提条件!$C$94,K53&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -15899,7 +15975,7 @@
       </c>
       <c r="R54" s="34" t="n">
         <f aca="false">IF(A54&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S54" s="34" t="n">
         <f aca="false">IF(A54=1,前提条件!$C$91,0)</f>
@@ -15959,15 +16035,15 @@
       </c>
       <c r="N55" s="72" t="n">
         <f aca="false">J55-M55-R55-S55</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O55" s="72" t="n">
         <f aca="false">O54+N55</f>
-        <v>6074196</v>
+        <v>5874196</v>
       </c>
       <c r="P55" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M55)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R55),0)</f>
-        <v>2700000</v>
+        <v>3000000</v>
       </c>
       <c r="Q55" s="73" t="str">
         <f aca="false">IF(AND(K55&gt;=前提条件!$C$94,K54&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -15975,7 +16051,7 @@
       </c>
       <c r="R55" s="34" t="n">
         <f aca="false">IF(A55&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S55" s="34" t="n">
         <f aca="false">IF(A55=1,前提条件!$C$91,0)</f>
@@ -16035,15 +16111,15 @@
       </c>
       <c r="N56" s="72" t="n">
         <f aca="false">J56-M56-R56-S56</f>
-        <v>112808</v>
+        <v>108641.333333333</v>
       </c>
       <c r="O56" s="72" t="n">
         <f aca="false">O55+N56</f>
-        <v>6187004</v>
+        <v>5982837.33333333</v>
       </c>
       <c r="P56" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M56)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R56),0)</f>
-        <v>2662500</v>
+        <v>2958333.33333333</v>
       </c>
       <c r="Q56" s="73" t="str">
         <f aca="false">IF(AND(K56&gt;=前提条件!$C$94,K55&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -16051,7 +16127,7 @@
       </c>
       <c r="R56" s="34" t="n">
         <f aca="false">IF(A56&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S56" s="34" t="n">
         <f aca="false">IF(A56=1,前提条件!$C$91,0)</f>
@@ -16111,15 +16187,15 @@
       </c>
       <c r="N57" s="72" t="n">
         <f aca="false">J57-M57-R57-S57</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O57" s="72" t="n">
         <f aca="false">O56+N57</f>
-        <v>6316720</v>
+        <v>6108386.66666666</v>
       </c>
       <c r="P57" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M57)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R57),0)</f>
-        <v>2625000</v>
+        <v>2916666.66666667</v>
       </c>
       <c r="Q57" s="73" t="str">
         <f aca="false">IF(AND(K57&gt;=前提条件!$C$94,K56&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -16127,7 +16203,7 @@
       </c>
       <c r="R57" s="34" t="n">
         <f aca="false">IF(A57&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S57" s="34" t="n">
         <f aca="false">IF(A57=1,前提条件!$C$91,0)</f>
@@ -16187,15 +16263,15 @@
       </c>
       <c r="N58" s="72" t="n">
         <f aca="false">J58-M58-R58-S58</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O58" s="72" t="n">
         <f aca="false">O57+N58</f>
-        <v>6440800</v>
+        <v>6228300</v>
       </c>
       <c r="P58" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M58)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R58),0)</f>
-        <v>2587500</v>
+        <v>2875000</v>
       </c>
       <c r="Q58" s="73" t="str">
         <f aca="false">IF(AND(K58&gt;=前提条件!$C$94,K57&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -16203,7 +16279,7 @@
       </c>
       <c r="R58" s="34" t="n">
         <f aca="false">IF(A58&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S58" s="34" t="n">
         <f aca="false">IF(A58=1,前提条件!$C$91,0)</f>
@@ -16263,15 +16339,15 @@
       </c>
       <c r="N59" s="72" t="n">
         <f aca="false">J59-M59-R59-S59</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O59" s="72" t="n">
         <f aca="false">O58+N59</f>
-        <v>6570516</v>
+        <v>6353849.33333333</v>
       </c>
       <c r="P59" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M59)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R59),0)</f>
-        <v>2550000</v>
+        <v>2833333.33333333</v>
       </c>
       <c r="Q59" s="73" t="str">
         <f aca="false">IF(AND(K59&gt;=前提条件!$C$94,K58&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -16279,7 +16355,7 @@
       </c>
       <c r="R59" s="34" t="n">
         <f aca="false">IF(A59&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S59" s="34" t="n">
         <f aca="false">IF(A59=1,前提条件!$C$91,0)</f>
@@ -16339,15 +16415,15 @@
       </c>
       <c r="N60" s="72" t="n">
         <f aca="false">J60-M60-R60-S60</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O60" s="72" t="n">
         <f aca="false">O59+N60</f>
-        <v>6694596</v>
+        <v>6473762.66666666</v>
       </c>
       <c r="P60" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M60)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R60),0)</f>
-        <v>2512500</v>
+        <v>2791666.66666667</v>
       </c>
       <c r="Q60" s="73" t="str">
         <f aca="false">IF(AND(K60&gt;=前提条件!$C$94,K59&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -16355,7 +16431,7 @@
       </c>
       <c r="R60" s="34" t="n">
         <f aca="false">IF(A60&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S60" s="34" t="n">
         <f aca="false">IF(A60=1,前提条件!$C$91,0)</f>
@@ -16415,15 +16491,15 @@
       </c>
       <c r="N61" s="72" t="n">
         <f aca="false">J61-M61-R61-S61</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O61" s="72" t="n">
         <f aca="false">O60+N61</f>
-        <v>6824312</v>
+        <v>6599312</v>
       </c>
       <c r="P61" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M61)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R61),0)</f>
-        <v>2475000</v>
+        <v>2750000</v>
       </c>
       <c r="Q61" s="73" t="str">
         <f aca="false">IF(AND(K61&gt;=前提条件!$C$94,K60&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -16431,7 +16507,7 @@
       </c>
       <c r="R61" s="34" t="n">
         <f aca="false">IF(A61&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S61" s="34" t="n">
         <f aca="false">IF(A61=1,前提条件!$C$91,0)</f>
@@ -16491,15 +16567,15 @@
       </c>
       <c r="N62" s="72" t="n">
         <f aca="false">J62-M62-R62-S62</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O62" s="72" t="n">
         <f aca="false">O61+N62</f>
-        <v>6954028</v>
+        <v>6724861.33333333</v>
       </c>
       <c r="P62" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M62)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R62),0)</f>
-        <v>2437500</v>
+        <v>2708333.33333333</v>
       </c>
       <c r="Q62" s="73" t="str">
         <f aca="false">IF(AND(K62&gt;=前提条件!$C$94,K61&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -16507,7 +16583,7 @@
       </c>
       <c r="R62" s="34" t="n">
         <f aca="false">IF(A62&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S62" s="34" t="n">
         <f aca="false">IF(A62=1,前提条件!$C$91,0)</f>
@@ -16567,15 +16643,15 @@
       </c>
       <c r="N63" s="72" t="n">
         <f aca="false">J63-M63-R63-S63</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O63" s="72" t="n">
         <f aca="false">O62+N63</f>
-        <v>7078108</v>
+        <v>6844774.66666666</v>
       </c>
       <c r="P63" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M63)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R63),0)</f>
-        <v>2400000</v>
+        <v>2666666.66666667</v>
       </c>
       <c r="Q63" s="73" t="str">
         <f aca="false">IF(AND(K63&gt;=前提条件!$C$94,K62&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -16583,7 +16659,7 @@
       </c>
       <c r="R63" s="34" t="n">
         <f aca="false">IF(A63&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S63" s="34" t="n">
         <f aca="false">IF(A63=1,前提条件!$C$91,0)</f>
@@ -16643,15 +16719,15 @@
       </c>
       <c r="N64" s="72" t="n">
         <f aca="false">J64-M64-R64-S64</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O64" s="72" t="n">
         <f aca="false">O63+N64</f>
-        <v>7207824</v>
+        <v>6970324</v>
       </c>
       <c r="P64" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M64)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R64),0)</f>
-        <v>2362500</v>
+        <v>2625000</v>
       </c>
       <c r="Q64" s="73" t="str">
         <f aca="false">IF(AND(K64&gt;=前提条件!$C$94,K63&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -16659,7 +16735,7 @@
       </c>
       <c r="R64" s="34" t="n">
         <f aca="false">IF(A64&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S64" s="34" t="n">
         <f aca="false">IF(A64=1,前提条件!$C$91,0)</f>
@@ -16719,15 +16795,15 @@
       </c>
       <c r="N65" s="72" t="n">
         <f aca="false">J65-M65-R65-S65</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O65" s="72" t="n">
         <f aca="false">O64+N65</f>
-        <v>7331904</v>
+        <v>7090237.33333333</v>
       </c>
       <c r="P65" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M65)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R65),0)</f>
-        <v>2325000</v>
+        <v>2583333.33333333</v>
       </c>
       <c r="Q65" s="73" t="str">
         <f aca="false">IF(AND(K65&gt;=前提条件!$C$94,K64&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -16735,7 +16811,7 @@
       </c>
       <c r="R65" s="34" t="n">
         <f aca="false">IF(A65&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S65" s="34" t="n">
         <f aca="false">IF(A65=1,前提条件!$C$91,0)</f>
@@ -16795,15 +16871,15 @@
       </c>
       <c r="N66" s="72" t="n">
         <f aca="false">J66-M66-R66-S66</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O66" s="72" t="n">
         <f aca="false">O65+N66</f>
-        <v>7461620</v>
+        <v>7215786.66666666</v>
       </c>
       <c r="P66" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M66)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R66),0)</f>
-        <v>2287500</v>
+        <v>2541666.66666667</v>
       </c>
       <c r="Q66" s="73" t="str">
         <f aca="false">IF(AND(K66&gt;=前提条件!$C$94,K65&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -16811,7 +16887,7 @@
       </c>
       <c r="R66" s="34" t="n">
         <f aca="false">IF(A66&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S66" s="34" t="n">
         <f aca="false">IF(A66=1,前提条件!$C$91,0)</f>
@@ -16871,15 +16947,15 @@
       </c>
       <c r="N67" s="72" t="n">
         <f aca="false">J67-M67-R67-S67</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O67" s="72" t="n">
         <f aca="false">O66+N67</f>
-        <v>7591336</v>
+        <v>7341335.99999999</v>
       </c>
       <c r="P67" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M67)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R67),0)</f>
-        <v>2250000</v>
+        <v>2500000</v>
       </c>
       <c r="Q67" s="73" t="str">
         <f aca="false">IF(AND(K67&gt;=前提条件!$C$94,K66&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -16887,7 +16963,7 @@
       </c>
       <c r="R67" s="34" t="n">
         <f aca="false">IF(A67&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S67" s="34" t="n">
         <f aca="false">IF(A67=1,前提条件!$C$91,0)</f>
@@ -16947,15 +17023,15 @@
       </c>
       <c r="N68" s="72" t="n">
         <f aca="false">J68-M68-R68-S68</f>
-        <v>118444</v>
+        <v>114277.333333333</v>
       </c>
       <c r="O68" s="72" t="n">
         <f aca="false">O67+N68</f>
-        <v>7709780</v>
+        <v>7455613.33333333</v>
       </c>
       <c r="P68" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M68)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R68),0)</f>
-        <v>2212500</v>
+        <v>2458333.33333333</v>
       </c>
       <c r="Q68" s="73" t="str">
         <f aca="false">IF(AND(K68&gt;=前提条件!$C$94,K67&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -16963,7 +17039,7 @@
       </c>
       <c r="R68" s="34" t="n">
         <f aca="false">IF(A68&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S68" s="34" t="n">
         <f aca="false">IF(A68=1,前提条件!$C$91,0)</f>
@@ -17023,15 +17099,15 @@
       </c>
       <c r="N69" s="72" t="n">
         <f aca="false">J69-M69-R69-S69</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O69" s="72" t="n">
         <f aca="false">O68+N69</f>
-        <v>7839496</v>
+        <v>7581162.66666666</v>
       </c>
       <c r="P69" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M69)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R69),0)</f>
-        <v>2175000</v>
+        <v>2416666.66666667</v>
       </c>
       <c r="Q69" s="73" t="str">
         <f aca="false">IF(AND(K69&gt;=前提条件!$C$94,K68&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -17039,7 +17115,7 @@
       </c>
       <c r="R69" s="34" t="n">
         <f aca="false">IF(A69&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S69" s="34" t="n">
         <f aca="false">IF(A69=1,前提条件!$C$91,0)</f>
@@ -17099,15 +17175,15 @@
       </c>
       <c r="N70" s="72" t="n">
         <f aca="false">J70-M70-R70-S70</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O70" s="72" t="n">
         <f aca="false">O69+N70</f>
-        <v>7963576</v>
+        <v>7701075.99999999</v>
       </c>
       <c r="P70" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M70)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R70),0)</f>
-        <v>2137500</v>
+        <v>2375000</v>
       </c>
       <c r="Q70" s="73" t="str">
         <f aca="false">IF(AND(K70&gt;=前提条件!$C$94,K69&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -17115,7 +17191,7 @@
       </c>
       <c r="R70" s="34" t="n">
         <f aca="false">IF(A70&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S70" s="34" t="n">
         <f aca="false">IF(A70=1,前提条件!$C$91,0)</f>
@@ -17175,15 +17251,15 @@
       </c>
       <c r="N71" s="72" t="n">
         <f aca="false">J71-M71-R71-S71</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O71" s="72" t="n">
         <f aca="false">O70+N71</f>
-        <v>8093292</v>
+        <v>7826625.33333333</v>
       </c>
       <c r="P71" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M71)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R71),0)</f>
-        <v>2100000</v>
+        <v>2333333.33333333</v>
       </c>
       <c r="Q71" s="73" t="str">
         <f aca="false">IF(AND(K71&gt;=前提条件!$C$94,K70&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -17191,7 +17267,7 @@
       </c>
       <c r="R71" s="34" t="n">
         <f aca="false">IF(A71&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S71" s="34" t="n">
         <f aca="false">IF(A71=1,前提条件!$C$91,0)</f>
@@ -17251,15 +17327,15 @@
       </c>
       <c r="N72" s="72" t="n">
         <f aca="false">J72-M72-R72-S72</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O72" s="72" t="n">
         <f aca="false">O71+N72</f>
-        <v>8217372</v>
+        <v>7946538.66666666</v>
       </c>
       <c r="P72" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M72)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R72),0)</f>
-        <v>2062500</v>
+        <v>2291666.66666667</v>
       </c>
       <c r="Q72" s="73" t="str">
         <f aca="false">IF(AND(K72&gt;=前提条件!$C$94,K71&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -17267,7 +17343,7 @@
       </c>
       <c r="R72" s="34" t="n">
         <f aca="false">IF(A72&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S72" s="34" t="n">
         <f aca="false">IF(A72=1,前提条件!$C$91,0)</f>
@@ -17327,15 +17403,15 @@
       </c>
       <c r="N73" s="72" t="n">
         <f aca="false">J73-M73-R73-S73</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O73" s="72" t="n">
         <f aca="false">O72+N73</f>
-        <v>8347088</v>
+        <v>8072087.99999999</v>
       </c>
       <c r="P73" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M73)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R73),0)</f>
-        <v>2025000</v>
+        <v>2250000</v>
       </c>
       <c r="Q73" s="73" t="str">
         <f aca="false">IF(AND(K73&gt;=前提条件!$C$94,K72&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -17343,7 +17419,7 @@
       </c>
       <c r="R73" s="34" t="n">
         <f aca="false">IF(A73&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S73" s="34" t="n">
         <f aca="false">IF(A73=1,前提条件!$C$91,0)</f>
@@ -17403,15 +17479,15 @@
       </c>
       <c r="N74" s="72" t="n">
         <f aca="false">J74-M74-R74-S74</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O74" s="72" t="n">
         <f aca="false">O73+N74</f>
-        <v>8476804</v>
+        <v>8197637.33333333</v>
       </c>
       <c r="P74" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M74)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R74),0)</f>
-        <v>1987500</v>
+        <v>2208333.33333333</v>
       </c>
       <c r="Q74" s="73" t="str">
         <f aca="false">IF(AND(K74&gt;=前提条件!$C$94,K73&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -17419,7 +17495,7 @@
       </c>
       <c r="R74" s="34" t="n">
         <f aca="false">IF(A74&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S74" s="34" t="n">
         <f aca="false">IF(A74=1,前提条件!$C$91,0)</f>
@@ -17479,15 +17555,15 @@
       </c>
       <c r="N75" s="72" t="n">
         <f aca="false">J75-M75-R75-S75</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O75" s="72" t="n">
         <f aca="false">O74+N75</f>
-        <v>8600884</v>
+        <v>8317550.66666666</v>
       </c>
       <c r="P75" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M75)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R75),0)</f>
-        <v>1950000</v>
+        <v>2166666.66666667</v>
       </c>
       <c r="Q75" s="73" t="str">
         <f aca="false">IF(AND(K75&gt;=前提条件!$C$94,K74&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -17495,7 +17571,7 @@
       </c>
       <c r="R75" s="34" t="n">
         <f aca="false">IF(A75&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S75" s="34" t="n">
         <f aca="false">IF(A75=1,前提条件!$C$91,0)</f>
@@ -17555,15 +17631,15 @@
       </c>
       <c r="N76" s="72" t="n">
         <f aca="false">J76-M76-R76-S76</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O76" s="72" t="n">
         <f aca="false">O75+N76</f>
-        <v>8730600</v>
+        <v>8443099.99999999</v>
       </c>
       <c r="P76" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M76)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R76),0)</f>
-        <v>1912500</v>
+        <v>2125000</v>
       </c>
       <c r="Q76" s="73" t="str">
         <f aca="false">IF(AND(K76&gt;=前提条件!$C$94,K75&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -17571,7 +17647,7 @@
       </c>
       <c r="R76" s="34" t="n">
         <f aca="false">IF(A76&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S76" s="34" t="n">
         <f aca="false">IF(A76=1,前提条件!$C$91,0)</f>
@@ -17631,15 +17707,15 @@
       </c>
       <c r="N77" s="72" t="n">
         <f aca="false">J77-M77-R77-S77</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O77" s="72" t="n">
         <f aca="false">O76+N77</f>
-        <v>8854680</v>
+        <v>8563013.33333333</v>
       </c>
       <c r="P77" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M77)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R77),0)</f>
-        <v>1875000</v>
+        <v>2083333.33333333</v>
       </c>
       <c r="Q77" s="73" t="str">
         <f aca="false">IF(AND(K77&gt;=前提条件!$C$94,K76&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -17647,7 +17723,7 @@
       </c>
       <c r="R77" s="34" t="n">
         <f aca="false">IF(A77&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S77" s="34" t="n">
         <f aca="false">IF(A77=1,前提条件!$C$91,0)</f>
@@ -17707,15 +17783,15 @@
       </c>
       <c r="N78" s="72" t="n">
         <f aca="false">J78-M78-R78-S78</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O78" s="72" t="n">
         <f aca="false">O77+N78</f>
-        <v>8984396</v>
+        <v>8688562.66666666</v>
       </c>
       <c r="P78" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M78)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R78),0)</f>
-        <v>1837500</v>
+        <v>2041666.66666667</v>
       </c>
       <c r="Q78" s="73" t="str">
         <f aca="false">IF(AND(K78&gt;=前提条件!$C$94,K77&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -17723,7 +17799,7 @@
       </c>
       <c r="R78" s="34" t="n">
         <f aca="false">IF(A78&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S78" s="34" t="n">
         <f aca="false">IF(A78=1,前提条件!$C$91,0)</f>
@@ -17783,15 +17859,15 @@
       </c>
       <c r="N79" s="72" t="n">
         <f aca="false">J79-M79-R79-S79</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O79" s="72" t="n">
         <f aca="false">O78+N79</f>
-        <v>9114112</v>
+        <v>8814111.99999999</v>
       </c>
       <c r="P79" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M79)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R79),0)</f>
-        <v>1800000</v>
+        <v>2000000</v>
       </c>
       <c r="Q79" s="73" t="str">
         <f aca="false">IF(AND(K79&gt;=前提条件!$C$94,K78&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -17799,7 +17875,7 @@
       </c>
       <c r="R79" s="34" t="n">
         <f aca="false">IF(A79&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S79" s="34" t="n">
         <f aca="false">IF(A79=1,前提条件!$C$91,0)</f>
@@ -17859,15 +17935,15 @@
       </c>
       <c r="N80" s="72" t="n">
         <f aca="false">J80-M80-R80-S80</f>
-        <v>112808</v>
+        <v>108641.333333333</v>
       </c>
       <c r="O80" s="72" t="n">
         <f aca="false">O79+N80</f>
-        <v>9226920</v>
+        <v>8922753.33333333</v>
       </c>
       <c r="P80" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M80)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R80),0)</f>
-        <v>1762500</v>
+        <v>1958333.33333333</v>
       </c>
       <c r="Q80" s="73" t="str">
         <f aca="false">IF(AND(K80&gt;=前提条件!$C$94,K79&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -17875,7 +17951,7 @@
       </c>
       <c r="R80" s="34" t="n">
         <f aca="false">IF(A80&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S80" s="34" t="n">
         <f aca="false">IF(A80=1,前提条件!$C$91,0)</f>
@@ -17935,15 +18011,15 @@
       </c>
       <c r="N81" s="72" t="n">
         <f aca="false">J81-M81-R81-S81</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O81" s="72" t="n">
         <f aca="false">O80+N81</f>
-        <v>9356636</v>
+        <v>9048302.66666666</v>
       </c>
       <c r="P81" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M81)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R81),0)</f>
-        <v>1725000</v>
+        <v>1916666.66666667</v>
       </c>
       <c r="Q81" s="73" t="str">
         <f aca="false">IF(AND(K81&gt;=前提条件!$C$94,K80&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -17951,7 +18027,7 @@
       </c>
       <c r="R81" s="34" t="n">
         <f aca="false">IF(A81&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S81" s="34" t="n">
         <f aca="false">IF(A81=1,前提条件!$C$91,0)</f>
@@ -18011,15 +18087,15 @@
       </c>
       <c r="N82" s="72" t="n">
         <f aca="false">J82-M82-R82-S82</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O82" s="72" t="n">
         <f aca="false">O81+N82</f>
-        <v>9480716</v>
+        <v>9168216</v>
       </c>
       <c r="P82" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M82)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R82),0)</f>
-        <v>1687500</v>
+        <v>1875000</v>
       </c>
       <c r="Q82" s="73" t="str">
         <f aca="false">IF(AND(K82&gt;=前提条件!$C$94,K81&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -18027,7 +18103,7 @@
       </c>
       <c r="R82" s="34" t="n">
         <f aca="false">IF(A82&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S82" s="34" t="n">
         <f aca="false">IF(A82=1,前提条件!$C$91,0)</f>
@@ -18087,15 +18163,15 @@
       </c>
       <c r="N83" s="72" t="n">
         <f aca="false">J83-M83-R83-S83</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O83" s="72" t="n">
         <f aca="false">O82+N83</f>
-        <v>9610432</v>
+        <v>9293765.33333333</v>
       </c>
       <c r="P83" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M83)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R83),0)</f>
-        <v>1650000</v>
+        <v>1833333.33333333</v>
       </c>
       <c r="Q83" s="73" t="str">
         <f aca="false">IF(AND(K83&gt;=前提条件!$C$94,K82&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -18103,7 +18179,7 @@
       </c>
       <c r="R83" s="34" t="n">
         <f aca="false">IF(A83&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S83" s="34" t="n">
         <f aca="false">IF(A83=1,前提条件!$C$91,0)</f>
@@ -18163,15 +18239,15 @@
       </c>
       <c r="N84" s="72" t="n">
         <f aca="false">J84-M84-R84-S84</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O84" s="72" t="n">
         <f aca="false">O83+N84</f>
-        <v>9734512</v>
+        <v>9413678.66666666</v>
       </c>
       <c r="P84" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M84)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R84),0)</f>
-        <v>1612500</v>
+        <v>1791666.66666667</v>
       </c>
       <c r="Q84" s="73" t="str">
         <f aca="false">IF(AND(K84&gt;=前提条件!$C$94,K83&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -18179,7 +18255,7 @@
       </c>
       <c r="R84" s="34" t="n">
         <f aca="false">IF(A84&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S84" s="34" t="n">
         <f aca="false">IF(A84=1,前提条件!$C$91,0)</f>
@@ -18239,15 +18315,15 @@
       </c>
       <c r="N85" s="72" t="n">
         <f aca="false">J85-M85-R85-S85</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O85" s="72" t="n">
         <f aca="false">O84+N85</f>
-        <v>9864228</v>
+        <v>9539228</v>
       </c>
       <c r="P85" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M85)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R85),0)</f>
-        <v>1575000</v>
+        <v>1750000</v>
       </c>
       <c r="Q85" s="73" t="str">
         <f aca="false">IF(AND(K85&gt;=前提条件!$C$94,K84&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -18255,7 +18331,7 @@
       </c>
       <c r="R85" s="34" t="n">
         <f aca="false">IF(A85&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S85" s="34" t="n">
         <f aca="false">IF(A85=1,前提条件!$C$91,0)</f>
@@ -18315,15 +18391,15 @@
       </c>
       <c r="N86" s="72" t="n">
         <f aca="false">J86-M86-R86-S86</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O86" s="72" t="n">
         <f aca="false">O85+N86</f>
-        <v>9993944</v>
+        <v>9664777.33333333</v>
       </c>
       <c r="P86" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M86)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R86),0)</f>
-        <v>1537500</v>
+        <v>1708333.33333333</v>
       </c>
       <c r="Q86" s="73" t="str">
         <f aca="false">IF(AND(K86&gt;=前提条件!$C$94,K85&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -18331,7 +18407,7 @@
       </c>
       <c r="R86" s="34" t="n">
         <f aca="false">IF(A86&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S86" s="34" t="n">
         <f aca="false">IF(A86=1,前提条件!$C$91,0)</f>
@@ -18391,15 +18467,15 @@
       </c>
       <c r="N87" s="72" t="n">
         <f aca="false">J87-M87-R87-S87</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O87" s="72" t="n">
         <f aca="false">O86+N87</f>
-        <v>10118024</v>
+        <v>9784690.66666667</v>
       </c>
       <c r="P87" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M87)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R87),0)</f>
-        <v>1500000</v>
+        <v>1666666.66666667</v>
       </c>
       <c r="Q87" s="73" t="str">
         <f aca="false">IF(AND(K87&gt;=前提条件!$C$94,K86&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -18407,7 +18483,7 @@
       </c>
       <c r="R87" s="34" t="n">
         <f aca="false">IF(A87&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S87" s="34" t="n">
         <f aca="false">IF(A87=1,前提条件!$C$91,0)</f>
@@ -18467,15 +18543,15 @@
       </c>
       <c r="N88" s="72" t="n">
         <f aca="false">J88-M88-R88-S88</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O88" s="72" t="n">
         <f aca="false">O87+N88</f>
-        <v>10247740</v>
+        <v>9910240</v>
       </c>
       <c r="P88" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M88)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R88),0)</f>
-        <v>1462500</v>
+        <v>1625000</v>
       </c>
       <c r="Q88" s="73" t="str">
         <f aca="false">IF(AND(K88&gt;=前提条件!$C$94,K87&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -18483,7 +18559,7 @@
       </c>
       <c r="R88" s="34" t="n">
         <f aca="false">IF(A88&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S88" s="34" t="n">
         <f aca="false">IF(A88=1,前提条件!$C$91,0)</f>
@@ -18543,15 +18619,15 @@
       </c>
       <c r="N89" s="72" t="n">
         <f aca="false">J89-M89-R89-S89</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O89" s="72" t="n">
         <f aca="false">O88+N89</f>
-        <v>10371820</v>
+        <v>10030153.3333333</v>
       </c>
       <c r="P89" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M89)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R89),0)</f>
-        <v>1425000</v>
+        <v>1583333.33333333</v>
       </c>
       <c r="Q89" s="73" t="str">
         <f aca="false">IF(AND(K89&gt;=前提条件!$C$94,K88&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -18559,7 +18635,7 @@
       </c>
       <c r="R89" s="34" t="n">
         <f aca="false">IF(A89&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S89" s="34" t="n">
         <f aca="false">IF(A89=1,前提条件!$C$91,0)</f>
@@ -18619,15 +18695,15 @@
       </c>
       <c r="N90" s="72" t="n">
         <f aca="false">J90-M90-R90-S90</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O90" s="72" t="n">
         <f aca="false">O89+N90</f>
-        <v>10501536</v>
+        <v>10155702.6666667</v>
       </c>
       <c r="P90" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M90)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R90),0)</f>
-        <v>1387500</v>
+        <v>1541666.66666667</v>
       </c>
       <c r="Q90" s="73" t="str">
         <f aca="false">IF(AND(K90&gt;=前提条件!$C$94,K89&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -18635,7 +18711,7 @@
       </c>
       <c r="R90" s="34" t="n">
         <f aca="false">IF(A90&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S90" s="34" t="n">
         <f aca="false">IF(A90=1,前提条件!$C$91,0)</f>
@@ -18695,15 +18771,15 @@
       </c>
       <c r="N91" s="72" t="n">
         <f aca="false">J91-M91-R91-S91</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O91" s="72" t="n">
         <f aca="false">O90+N91</f>
-        <v>10631252</v>
+        <v>10281252</v>
       </c>
       <c r="P91" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M91)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R91),0)</f>
-        <v>1350000</v>
+        <v>1500000</v>
       </c>
       <c r="Q91" s="73" t="str">
         <f aca="false">IF(AND(K91&gt;=前提条件!$C$94,K90&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -18711,7 +18787,7 @@
       </c>
       <c r="R91" s="34" t="n">
         <f aca="false">IF(A91&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S91" s="34" t="n">
         <f aca="false">IF(A91=1,前提条件!$C$91,0)</f>
@@ -18771,15 +18847,15 @@
       </c>
       <c r="N92" s="72" t="n">
         <f aca="false">J92-M92-R92-S92</f>
-        <v>112808</v>
+        <v>108641.333333333</v>
       </c>
       <c r="O92" s="72" t="n">
         <f aca="false">O91+N92</f>
-        <v>10744060</v>
+        <v>10389893.3333333</v>
       </c>
       <c r="P92" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M92)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R92),0)</f>
-        <v>1312500</v>
+        <v>1458333.33333333</v>
       </c>
       <c r="Q92" s="73" t="str">
         <f aca="false">IF(AND(K92&gt;=前提条件!$C$94,K91&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -18787,7 +18863,7 @@
       </c>
       <c r="R92" s="34" t="n">
         <f aca="false">IF(A92&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S92" s="34" t="n">
         <f aca="false">IF(A92=1,前提条件!$C$91,0)</f>
@@ -18847,15 +18923,15 @@
       </c>
       <c r="N93" s="72" t="n">
         <f aca="false">J93-M93-R93-S93</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O93" s="72" t="n">
         <f aca="false">O92+N93</f>
-        <v>10873776</v>
+        <v>10515442.6666667</v>
       </c>
       <c r="P93" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M93)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R93),0)</f>
-        <v>1275000</v>
+        <v>1416666.66666667</v>
       </c>
       <c r="Q93" s="73" t="str">
         <f aca="false">IF(AND(K93&gt;=前提条件!$C$94,K92&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -18863,7 +18939,7 @@
       </c>
       <c r="R93" s="34" t="n">
         <f aca="false">IF(A93&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S93" s="34" t="n">
         <f aca="false">IF(A93=1,前提条件!$C$91,0)</f>
@@ -18923,15 +18999,15 @@
       </c>
       <c r="N94" s="72" t="n">
         <f aca="false">J94-M94-R94-S94</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O94" s="72" t="n">
         <f aca="false">O93+N94</f>
-        <v>10997856</v>
+        <v>10635356</v>
       </c>
       <c r="P94" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M94)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R94),0)</f>
-        <v>1237500</v>
+        <v>1375000</v>
       </c>
       <c r="Q94" s="73" t="str">
         <f aca="false">IF(AND(K94&gt;=前提条件!$C$94,K93&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -18939,7 +19015,7 @@
       </c>
       <c r="R94" s="34" t="n">
         <f aca="false">IF(A94&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S94" s="34" t="n">
         <f aca="false">IF(A94=1,前提条件!$C$91,0)</f>
@@ -18999,15 +19075,15 @@
       </c>
       <c r="N95" s="72" t="n">
         <f aca="false">J95-M95-R95-S95</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O95" s="72" t="n">
         <f aca="false">O94+N95</f>
-        <v>11127572</v>
+        <v>10760905.3333333</v>
       </c>
       <c r="P95" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M95)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R95),0)</f>
-        <v>1200000</v>
+        <v>1333333.33333333</v>
       </c>
       <c r="Q95" s="73" t="str">
         <f aca="false">IF(AND(K95&gt;=前提条件!$C$94,K94&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -19015,7 +19091,7 @@
       </c>
       <c r="R95" s="34" t="n">
         <f aca="false">IF(A95&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S95" s="34" t="n">
         <f aca="false">IF(A95=1,前提条件!$C$91,0)</f>
@@ -19075,15 +19151,15 @@
       </c>
       <c r="N96" s="72" t="n">
         <f aca="false">J96-M96-R96-S96</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O96" s="72" t="n">
         <f aca="false">O95+N96</f>
-        <v>11251652</v>
+        <v>10880818.6666667</v>
       </c>
       <c r="P96" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M96)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R96),0)</f>
-        <v>1162500</v>
+        <v>1291666.66666667</v>
       </c>
       <c r="Q96" s="73" t="str">
         <f aca="false">IF(AND(K96&gt;=前提条件!$C$94,K95&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -19091,7 +19167,7 @@
       </c>
       <c r="R96" s="34" t="n">
         <f aca="false">IF(A96&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S96" s="34" t="n">
         <f aca="false">IF(A96=1,前提条件!$C$91,0)</f>
@@ -19151,15 +19227,15 @@
       </c>
       <c r="N97" s="72" t="n">
         <f aca="false">J97-M97-R97-S97</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O97" s="72" t="n">
         <f aca="false">O96+N97</f>
-        <v>11381368</v>
+        <v>11006368</v>
       </c>
       <c r="P97" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M97)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R97),0)</f>
-        <v>1125000</v>
+        <v>1250000</v>
       </c>
       <c r="Q97" s="73" t="str">
         <f aca="false">IF(AND(K97&gt;=前提条件!$C$94,K96&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -19167,7 +19243,7 @@
       </c>
       <c r="R97" s="34" t="n">
         <f aca="false">IF(A97&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S97" s="34" t="n">
         <f aca="false">IF(A97=1,前提条件!$C$91,0)</f>
@@ -19227,15 +19303,15 @@
       </c>
       <c r="N98" s="72" t="n">
         <f aca="false">J98-M98-R98-S98</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O98" s="72" t="n">
         <f aca="false">O97+N98</f>
-        <v>11511084</v>
+        <v>11131917.3333333</v>
       </c>
       <c r="P98" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M98)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R98),0)</f>
-        <v>1087500</v>
+        <v>1208333.33333333</v>
       </c>
       <c r="Q98" s="73" t="str">
         <f aca="false">IF(AND(K98&gt;=前提条件!$C$94,K97&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -19243,7 +19319,7 @@
       </c>
       <c r="R98" s="34" t="n">
         <f aca="false">IF(A98&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S98" s="34" t="n">
         <f aca="false">IF(A98=1,前提条件!$C$91,0)</f>
@@ -19303,15 +19379,15 @@
       </c>
       <c r="N99" s="72" t="n">
         <f aca="false">J99-M99-R99-S99</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O99" s="72" t="n">
         <f aca="false">O98+N99</f>
-        <v>11635164</v>
+        <v>11251830.6666667</v>
       </c>
       <c r="P99" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M99)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R99),0)</f>
-        <v>1050000</v>
+        <v>1166666.66666667</v>
       </c>
       <c r="Q99" s="73" t="str">
         <f aca="false">IF(AND(K99&gt;=前提条件!$C$94,K98&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -19319,7 +19395,7 @@
       </c>
       <c r="R99" s="34" t="n">
         <f aca="false">IF(A99&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S99" s="34" t="n">
         <f aca="false">IF(A99=1,前提条件!$C$91,0)</f>
@@ -19379,15 +19455,15 @@
       </c>
       <c r="N100" s="72" t="n">
         <f aca="false">J100-M100-R100-S100</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O100" s="72" t="n">
         <f aca="false">O99+N100</f>
-        <v>11764880</v>
+        <v>11377380</v>
       </c>
       <c r="P100" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M100)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R100),0)</f>
-        <v>1012500</v>
+        <v>1125000</v>
       </c>
       <c r="Q100" s="73" t="str">
         <f aca="false">IF(AND(K100&gt;=前提条件!$C$94,K99&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -19395,7 +19471,7 @@
       </c>
       <c r="R100" s="34" t="n">
         <f aca="false">IF(A100&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S100" s="34" t="n">
         <f aca="false">IF(A100=1,前提条件!$C$91,0)</f>
@@ -19455,15 +19531,15 @@
       </c>
       <c r="N101" s="72" t="n">
         <f aca="false">J101-M101-R101-S101</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O101" s="72" t="n">
         <f aca="false">O100+N101</f>
-        <v>11888960</v>
+        <v>11497293.3333333</v>
       </c>
       <c r="P101" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M101)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R101),0)</f>
-        <v>975000</v>
+        <v>1083333.33333333</v>
       </c>
       <c r="Q101" s="73" t="str">
         <f aca="false">IF(AND(K101&gt;=前提条件!$C$94,K100&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -19471,7 +19547,7 @@
       </c>
       <c r="R101" s="34" t="n">
         <f aca="false">IF(A101&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S101" s="34" t="n">
         <f aca="false">IF(A101=1,前提条件!$C$91,0)</f>
@@ -19531,15 +19607,15 @@
       </c>
       <c r="N102" s="72" t="n">
         <f aca="false">J102-M102-R102-S102</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O102" s="72" t="n">
         <f aca="false">O101+N102</f>
-        <v>12018676</v>
+        <v>11622842.6666667</v>
       </c>
       <c r="P102" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M102)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R102),0)</f>
-        <v>937500</v>
+        <v>1041666.66666667</v>
       </c>
       <c r="Q102" s="73" t="str">
         <f aca="false">IF(AND(K102&gt;=前提条件!$C$94,K101&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -19547,7 +19623,7 @@
       </c>
       <c r="R102" s="34" t="n">
         <f aca="false">IF(A102&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S102" s="34" t="n">
         <f aca="false">IF(A102=1,前提条件!$C$91,0)</f>
@@ -19607,15 +19683,15 @@
       </c>
       <c r="N103" s="72" t="n">
         <f aca="false">J103-M103-R103-S103</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O103" s="72" t="n">
         <f aca="false">O102+N103</f>
-        <v>12148392</v>
+        <v>11748392</v>
       </c>
       <c r="P103" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M103)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R103),0)</f>
-        <v>900000</v>
+        <v>1000000</v>
       </c>
       <c r="Q103" s="73" t="str">
         <f aca="false">IF(AND(K103&gt;=前提条件!$C$94,K102&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -19623,7 +19699,7 @@
       </c>
       <c r="R103" s="34" t="n">
         <f aca="false">IF(A103&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S103" s="34" t="n">
         <f aca="false">IF(A103=1,前提条件!$C$91,0)</f>
@@ -19683,15 +19759,15 @@
       </c>
       <c r="N104" s="72" t="n">
         <f aca="false">J104-M104-R104-S104</f>
-        <v>112808</v>
+        <v>108641.333333333</v>
       </c>
       <c r="O104" s="72" t="n">
         <f aca="false">O103+N104</f>
-        <v>12261200</v>
+        <v>11857033.3333333</v>
       </c>
       <c r="P104" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M104)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R104),0)</f>
-        <v>862500</v>
+        <v>958333.333333333</v>
       </c>
       <c r="Q104" s="73" t="str">
         <f aca="false">IF(AND(K104&gt;=前提条件!$C$94,K103&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -19699,7 +19775,7 @@
       </c>
       <c r="R104" s="34" t="n">
         <f aca="false">IF(A104&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S104" s="34" t="n">
         <f aca="false">IF(A104=1,前提条件!$C$91,0)</f>
@@ -19759,15 +19835,15 @@
       </c>
       <c r="N105" s="72" t="n">
         <f aca="false">J105-M105-R105-S105</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O105" s="72" t="n">
         <f aca="false">O104+N105</f>
-        <v>12390916</v>
+        <v>11982582.6666667</v>
       </c>
       <c r="P105" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M105)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R105),0)</f>
-        <v>825000</v>
+        <v>916666.666666667</v>
       </c>
       <c r="Q105" s="73" t="str">
         <f aca="false">IF(AND(K105&gt;=前提条件!$C$94,K104&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -19775,7 +19851,7 @@
       </c>
       <c r="R105" s="34" t="n">
         <f aca="false">IF(A105&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S105" s="34" t="n">
         <f aca="false">IF(A105=1,前提条件!$C$91,0)</f>
@@ -19835,15 +19911,15 @@
       </c>
       <c r="N106" s="72" t="n">
         <f aca="false">J106-M106-R106-S106</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O106" s="72" t="n">
         <f aca="false">O105+N106</f>
-        <v>12514996</v>
+        <v>12102496</v>
       </c>
       <c r="P106" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M106)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R106),0)</f>
-        <v>787500</v>
+        <v>875000</v>
       </c>
       <c r="Q106" s="73" t="str">
         <f aca="false">IF(AND(K106&gt;=前提条件!$C$94,K105&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -19851,7 +19927,7 @@
       </c>
       <c r="R106" s="34" t="n">
         <f aca="false">IF(A106&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S106" s="34" t="n">
         <f aca="false">IF(A106=1,前提条件!$C$91,0)</f>
@@ -19911,15 +19987,15 @@
       </c>
       <c r="N107" s="72" t="n">
         <f aca="false">J107-M107-R107-S107</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O107" s="72" t="n">
         <f aca="false">O106+N107</f>
-        <v>12644712</v>
+        <v>12228045.3333333</v>
       </c>
       <c r="P107" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M107)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R107),0)</f>
-        <v>750000</v>
+        <v>833333.333333333</v>
       </c>
       <c r="Q107" s="73" t="str">
         <f aca="false">IF(AND(K107&gt;=前提条件!$C$94,K106&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -19927,7 +20003,7 @@
       </c>
       <c r="R107" s="34" t="n">
         <f aca="false">IF(A107&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S107" s="34" t="n">
         <f aca="false">IF(A107=1,前提条件!$C$91,0)</f>
@@ -19987,15 +20063,15 @@
       </c>
       <c r="N108" s="72" t="n">
         <f aca="false">J108-M108-R108-S108</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O108" s="72" t="n">
         <f aca="false">O107+N108</f>
-        <v>12768792</v>
+        <v>12347958.6666667</v>
       </c>
       <c r="P108" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M108)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R108),0)</f>
-        <v>712500</v>
+        <v>791666.666666667</v>
       </c>
       <c r="Q108" s="73" t="str">
         <f aca="false">IF(AND(K108&gt;=前提条件!$C$94,K107&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -20003,7 +20079,7 @@
       </c>
       <c r="R108" s="34" t="n">
         <f aca="false">IF(A108&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S108" s="34" t="n">
         <f aca="false">IF(A108=1,前提条件!$C$91,0)</f>
@@ -20063,15 +20139,15 @@
       </c>
       <c r="N109" s="72" t="n">
         <f aca="false">J109-M109-R109-S109</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O109" s="72" t="n">
         <f aca="false">O108+N109</f>
-        <v>12898508</v>
+        <v>12473508</v>
       </c>
       <c r="P109" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M109)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R109),0)</f>
-        <v>675000</v>
+        <v>750000</v>
       </c>
       <c r="Q109" s="73" t="str">
         <f aca="false">IF(AND(K109&gt;=前提条件!$C$94,K108&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -20079,7 +20155,7 @@
       </c>
       <c r="R109" s="34" t="n">
         <f aca="false">IF(A109&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S109" s="34" t="n">
         <f aca="false">IF(A109=1,前提条件!$C$91,0)</f>
@@ -20139,15 +20215,15 @@
       </c>
       <c r="N110" s="72" t="n">
         <f aca="false">J110-M110-R110-S110</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O110" s="72" t="n">
         <f aca="false">O109+N110</f>
-        <v>13028224</v>
+        <v>12599057.3333333</v>
       </c>
       <c r="P110" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M110)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R110),0)</f>
-        <v>637500</v>
+        <v>708333.333333333</v>
       </c>
       <c r="Q110" s="73" t="str">
         <f aca="false">IF(AND(K110&gt;=前提条件!$C$94,K109&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -20155,7 +20231,7 @@
       </c>
       <c r="R110" s="34" t="n">
         <f aca="false">IF(A110&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S110" s="34" t="n">
         <f aca="false">IF(A110=1,前提条件!$C$91,0)</f>
@@ -20215,15 +20291,15 @@
       </c>
       <c r="N111" s="72" t="n">
         <f aca="false">J111-M111-R111-S111</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O111" s="72" t="n">
         <f aca="false">O110+N111</f>
-        <v>13152304</v>
+        <v>12718970.6666667</v>
       </c>
       <c r="P111" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M111)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R111),0)</f>
-        <v>600000</v>
+        <v>666666.666666667</v>
       </c>
       <c r="Q111" s="73" t="str">
         <f aca="false">IF(AND(K111&gt;=前提条件!$C$94,K110&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -20231,7 +20307,7 @@
       </c>
       <c r="R111" s="34" t="n">
         <f aca="false">IF(A111&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S111" s="34" t="n">
         <f aca="false">IF(A111=1,前提条件!$C$91,0)</f>
@@ -20291,15 +20367,15 @@
       </c>
       <c r="N112" s="72" t="n">
         <f aca="false">J112-M112-R112-S112</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O112" s="72" t="n">
         <f aca="false">O111+N112</f>
-        <v>13282020</v>
+        <v>12844520</v>
       </c>
       <c r="P112" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M112)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R112),0)</f>
-        <v>562500</v>
+        <v>625000</v>
       </c>
       <c r="Q112" s="73" t="str">
         <f aca="false">IF(AND(K112&gt;=前提条件!$C$94,K111&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -20307,7 +20383,7 @@
       </c>
       <c r="R112" s="34" t="n">
         <f aca="false">IF(A112&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S112" s="34" t="n">
         <f aca="false">IF(A112=1,前提条件!$C$91,0)</f>
@@ -20367,15 +20443,15 @@
       </c>
       <c r="N113" s="72" t="n">
         <f aca="false">J113-M113-R113-S113</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O113" s="72" t="n">
         <f aca="false">O112+N113</f>
-        <v>13406100</v>
+        <v>12964433.3333333</v>
       </c>
       <c r="P113" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M113)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R113),0)</f>
-        <v>525000</v>
+        <v>583333.333333333</v>
       </c>
       <c r="Q113" s="73" t="str">
         <f aca="false">IF(AND(K113&gt;=前提条件!$C$94,K112&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -20383,7 +20459,7 @@
       </c>
       <c r="R113" s="34" t="n">
         <f aca="false">IF(A113&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S113" s="34" t="n">
         <f aca="false">IF(A113=1,前提条件!$C$91,0)</f>
@@ -20443,15 +20519,15 @@
       </c>
       <c r="N114" s="72" t="n">
         <f aca="false">J114-M114-R114-S114</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O114" s="72" t="n">
         <f aca="false">O113+N114</f>
-        <v>13535816</v>
+        <v>13089982.6666667</v>
       </c>
       <c r="P114" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M114)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R114),0)</f>
-        <v>487500</v>
+        <v>541666.666666667</v>
       </c>
       <c r="Q114" s="73" t="str">
         <f aca="false">IF(AND(K114&gt;=前提条件!$C$94,K113&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -20459,7 +20535,7 @@
       </c>
       <c r="R114" s="34" t="n">
         <f aca="false">IF(A114&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S114" s="34" t="n">
         <f aca="false">IF(A114=1,前提条件!$C$91,0)</f>
@@ -20519,15 +20595,15 @@
       </c>
       <c r="N115" s="72" t="n">
         <f aca="false">J115-M115-R115-S115</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O115" s="72" t="n">
         <f aca="false">O114+N115</f>
-        <v>13665532</v>
+        <v>13215532</v>
       </c>
       <c r="P115" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M115)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R115),0)</f>
-        <v>450000</v>
+        <v>500000</v>
       </c>
       <c r="Q115" s="73" t="str">
         <f aca="false">IF(AND(K115&gt;=前提条件!$C$94,K114&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -20535,7 +20611,7 @@
       </c>
       <c r="R115" s="34" t="n">
         <f aca="false">IF(A115&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S115" s="34" t="n">
         <f aca="false">IF(A115=1,前提条件!$C$91,0)</f>
@@ -20595,15 +20671,15 @@
       </c>
       <c r="N116" s="72" t="n">
         <f aca="false">J116-M116-R116-S116</f>
-        <v>118444</v>
+        <v>114277.333333333</v>
       </c>
       <c r="O116" s="72" t="n">
         <f aca="false">O115+N116</f>
-        <v>13783976</v>
+        <v>13329809.3333334</v>
       </c>
       <c r="P116" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M116)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R116),0)</f>
-        <v>412500</v>
+        <v>458333.333333333</v>
       </c>
       <c r="Q116" s="73" t="str">
         <f aca="false">IF(AND(K116&gt;=前提条件!$C$94,K115&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -20611,7 +20687,7 @@
       </c>
       <c r="R116" s="34" t="n">
         <f aca="false">IF(A116&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S116" s="34" t="n">
         <f aca="false">IF(A116=1,前提条件!$C$91,0)</f>
@@ -20671,15 +20747,15 @@
       </c>
       <c r="N117" s="72" t="n">
         <f aca="false">J117-M117-R117-S117</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O117" s="72" t="n">
         <f aca="false">O116+N117</f>
-        <v>13913692</v>
+        <v>13455358.6666667</v>
       </c>
       <c r="P117" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M117)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R117),0)</f>
-        <v>375000</v>
+        <v>416666.666666667</v>
       </c>
       <c r="Q117" s="73" t="str">
         <f aca="false">IF(AND(K117&gt;=前提条件!$C$94,K116&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -20687,7 +20763,7 @@
       </c>
       <c r="R117" s="34" t="n">
         <f aca="false">IF(A117&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S117" s="34" t="n">
         <f aca="false">IF(A117=1,前提条件!$C$91,0)</f>
@@ -20747,15 +20823,15 @@
       </c>
       <c r="N118" s="72" t="n">
         <f aca="false">J118-M118-R118-S118</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O118" s="72" t="n">
         <f aca="false">O117+N118</f>
-        <v>14037772</v>
+        <v>13575272</v>
       </c>
       <c r="P118" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M118)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R118),0)</f>
-        <v>337500</v>
+        <v>375000</v>
       </c>
       <c r="Q118" s="73" t="str">
         <f aca="false">IF(AND(K118&gt;=前提条件!$C$94,K117&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -20763,7 +20839,7 @@
       </c>
       <c r="R118" s="34" t="n">
         <f aca="false">IF(A118&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S118" s="34" t="n">
         <f aca="false">IF(A118=1,前提条件!$C$91,0)</f>
@@ -20823,15 +20899,15 @@
       </c>
       <c r="N119" s="72" t="n">
         <f aca="false">J119-M119-R119-S119</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O119" s="72" t="n">
         <f aca="false">O118+N119</f>
-        <v>14167488</v>
+        <v>13700821.3333334</v>
       </c>
       <c r="P119" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M119)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R119),0)</f>
-        <v>300000</v>
+        <v>333333.333333333</v>
       </c>
       <c r="Q119" s="73" t="str">
         <f aca="false">IF(AND(K119&gt;=前提条件!$C$94,K118&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -20839,7 +20915,7 @@
       </c>
       <c r="R119" s="34" t="n">
         <f aca="false">IF(A119&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S119" s="34" t="n">
         <f aca="false">IF(A119=1,前提条件!$C$91,0)</f>
@@ -20899,15 +20975,15 @@
       </c>
       <c r="N120" s="72" t="n">
         <f aca="false">J120-M120-R120-S120</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O120" s="72" t="n">
         <f aca="false">O119+N120</f>
-        <v>14291568</v>
+        <v>13820734.6666667</v>
       </c>
       <c r="P120" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M120)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R120),0)</f>
-        <v>262500</v>
+        <v>291666.666666667</v>
       </c>
       <c r="Q120" s="73" t="str">
         <f aca="false">IF(AND(K120&gt;=前提条件!$C$94,K119&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -20915,7 +20991,7 @@
       </c>
       <c r="R120" s="34" t="n">
         <f aca="false">IF(A120&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S120" s="34" t="n">
         <f aca="false">IF(A120=1,前提条件!$C$91,0)</f>
@@ -20975,15 +21051,15 @@
       </c>
       <c r="N121" s="72" t="n">
         <f aca="false">J121-M121-R121-S121</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O121" s="72" t="n">
         <f aca="false">O120+N121</f>
-        <v>14421284</v>
+        <v>13946284</v>
       </c>
       <c r="P121" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M121)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R121),0)</f>
-        <v>225000</v>
+        <v>250000</v>
       </c>
       <c r="Q121" s="73" t="str">
         <f aca="false">IF(AND(K121&gt;=前提条件!$C$94,K120&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -20991,7 +21067,7 @@
       </c>
       <c r="R121" s="34" t="n">
         <f aca="false">IF(A121&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S121" s="34" t="n">
         <f aca="false">IF(A121=1,前提条件!$C$91,0)</f>
@@ -21051,15 +21127,15 @@
       </c>
       <c r="N122" s="72" t="n">
         <f aca="false">J122-M122-R122-S122</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O122" s="72" t="n">
         <f aca="false">O121+N122</f>
-        <v>14551000</v>
+        <v>14071833.3333334</v>
       </c>
       <c r="P122" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M122)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R122),0)</f>
-        <v>187500</v>
+        <v>208333.333333333</v>
       </c>
       <c r="Q122" s="73" t="str">
         <f aca="false">IF(AND(K122&gt;=前提条件!$C$94,K121&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -21067,7 +21143,7 @@
       </c>
       <c r="R122" s="34" t="n">
         <f aca="false">IF(A122&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S122" s="34" t="n">
         <f aca="false">IF(A122=1,前提条件!$C$91,0)</f>
@@ -21127,15 +21203,15 @@
       </c>
       <c r="N123" s="72" t="n">
         <f aca="false">J123-M123-R123-S123</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O123" s="72" t="n">
         <f aca="false">O122+N123</f>
-        <v>14675080</v>
+        <v>14191746.6666667</v>
       </c>
       <c r="P123" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M123)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R123),0)</f>
-        <v>150000</v>
+        <v>166666.666666667</v>
       </c>
       <c r="Q123" s="73" t="str">
         <f aca="false">IF(AND(K123&gt;=前提条件!$C$94,K122&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -21143,7 +21219,7 @@
       </c>
       <c r="R123" s="34" t="n">
         <f aca="false">IF(A123&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S123" s="34" t="n">
         <f aca="false">IF(A123=1,前提条件!$C$91,0)</f>
@@ -21203,15 +21279,15 @@
       </c>
       <c r="N124" s="72" t="n">
         <f aca="false">J124-M124-R124-S124</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O124" s="72" t="n">
         <f aca="false">O123+N124</f>
-        <v>14804796</v>
+        <v>14317296</v>
       </c>
       <c r="P124" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M124)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R124),0)</f>
-        <v>112500</v>
+        <v>125000</v>
       </c>
       <c r="Q124" s="73" t="str">
         <f aca="false">IF(AND(K124&gt;=前提条件!$C$94,K123&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -21219,7 +21295,7 @@
       </c>
       <c r="R124" s="34" t="n">
         <f aca="false">IF(A124&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S124" s="34" t="n">
         <f aca="false">IF(A124=1,前提条件!$C$91,0)</f>
@@ -21279,15 +21355,15 @@
       </c>
       <c r="N125" s="72" t="n">
         <f aca="false">J125-M125-R125-S125</f>
-        <v>124080</v>
+        <v>119913.333333333</v>
       </c>
       <c r="O125" s="72" t="n">
         <f aca="false">O124+N125</f>
-        <v>14928876</v>
+        <v>14437209.3333334</v>
       </c>
       <c r="P125" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M125)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R125),0)</f>
-        <v>75000</v>
+        <v>83333.3333333333</v>
       </c>
       <c r="Q125" s="73" t="str">
         <f aca="false">IF(AND(K125&gt;=前提条件!$C$94,K124&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -21295,7 +21371,7 @@
       </c>
       <c r="R125" s="34" t="n">
         <f aca="false">IF(A125&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S125" s="34" t="n">
         <f aca="false">IF(A125=1,前提条件!$C$91,0)</f>
@@ -21355,15 +21431,15 @@
       </c>
       <c r="N126" s="72" t="n">
         <f aca="false">J126-M126-R126-S126</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O126" s="72" t="n">
         <f aca="false">O125+N126</f>
-        <v>15058592</v>
+        <v>14562758.6666667</v>
       </c>
       <c r="P126" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M126)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R126),0)</f>
-        <v>37500</v>
+        <v>41666.6666666666</v>
       </c>
       <c r="Q126" s="73" t="str">
         <f aca="false">IF(AND(K126&gt;=前提条件!$C$94,K125&lt;前提条件!$C$94),"◀投資回収","")</f>
@@ -21371,7 +21447,7 @@
       </c>
       <c r="R126" s="34" t="n">
         <f aca="false">IF(A126&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S126" s="34" t="n">
         <f aca="false">IF(A126=1,前提条件!$C$91,0)</f>
@@ -21431,11 +21507,11 @@
       </c>
       <c r="N127" s="72" t="n">
         <f aca="false">J127-M127-R127-S127</f>
-        <v>129716</v>
+        <v>125549.333333333</v>
       </c>
       <c r="O127" s="72" t="n">
         <f aca="false">O126+N127</f>
-        <v>15188308</v>
+        <v>14688308</v>
       </c>
       <c r="P127" s="72" t="n">
         <f aca="false">前提条件!$C$8-SUM(M$8:M127)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(R$8:R127),0)</f>
@@ -21447,7 +21523,7 @@
       </c>
       <c r="R127" s="34" t="n">
         <f aca="false">IF(A127&lt;=前提条件!$C$89*12,前提条件!$C$90,0)</f>
-        <v>0</v>
+        <v>4166.66666666667</v>
       </c>
       <c r="S127" s="34" t="n">
         <f aca="false">IF(A127=1,前提条件!$C$91,0)</f>
@@ -21559,7 +21635,7 @@
       </c>
       <c r="G5" s="29" t="n">
         <f aca="false">SUMIFS(投資回収_月次!$R$8:$R$127,投資回収_月次!$C$8:$C$127,B5)</f>
-        <v>0</v>
+        <v>20833.3333333333</v>
       </c>
       <c r="H5" s="29" t="n">
         <f aca="false">SUMIFS(投資回収_月次!$S$8:$S$127,投資回収_月次!$C$8:$C$127,B5)</f>
@@ -21567,7 +21643,7 @@
       </c>
       <c r="I5" s="39" t="n">
         <f aca="false">E5-F5-G5-H5</f>
-        <v>620400</v>
+        <v>599566.666666667</v>
       </c>
       <c r="J5" s="39" t="n">
         <f aca="false">SUM(E$5:E5)</f>
@@ -21575,15 +21651,15 @@
       </c>
       <c r="K5" s="39" t="n">
         <f aca="false">MAX(前提条件!$C$94-J5,0)</f>
-        <v>3692100</v>
+        <v>4192100</v>
       </c>
       <c r="L5" s="39" t="n">
         <f aca="false">前提条件!$C$8-SUM(F$5:F5)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(G$5:G5),0)</f>
-        <v>4312500</v>
+        <v>4791666.66666667</v>
       </c>
       <c r="M5" s="39" t="n">
         <f aca="false">SUM(I$5:I5)</f>
-        <v>620400</v>
+        <v>599566.666666667</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21608,7 +21684,7 @@
       </c>
       <c r="G6" s="29" t="n">
         <f aca="false">SUMIFS(投資回収_月次!$R$8:$R$127,投資回収_月次!$C$8:$C$127,B6)</f>
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="H6" s="29" t="n">
         <f aca="false">SUMIFS(投資回収_月次!$S$8:$S$127,投資回収_月次!$C$8:$C$127,B6)</f>
@@ -21616,7 +21692,7 @@
       </c>
       <c r="I6" s="39" t="n">
         <f aca="false">E6-F6-G6-H6</f>
-        <v>1522776</v>
+        <v>1472776</v>
       </c>
       <c r="J6" s="39" t="n">
         <f aca="false">SUM(E$5:E6)</f>
@@ -21624,15 +21700,15 @@
       </c>
       <c r="K6" s="39" t="n">
         <f aca="false">MAX(前提条件!$C$94-J6,0)</f>
-        <v>1719324</v>
+        <v>2219324</v>
       </c>
       <c r="L6" s="39" t="n">
         <f aca="false">前提条件!$C$8-SUM(F$5:F6)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(G$5:G6),0)</f>
-        <v>3862500</v>
+        <v>4291666.66666667</v>
       </c>
       <c r="M6" s="39" t="n">
         <f aca="false">SUM(I$5:I6)</f>
-        <v>2143176</v>
+        <v>2072342.66666667</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21657,7 +21733,7 @@
       </c>
       <c r="G7" s="29" t="n">
         <f aca="false">SUMIFS(投資回収_月次!$R$8:$R$127,投資回収_月次!$C$8:$C$127,B7)</f>
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="H7" s="29" t="n">
         <f aca="false">SUMIFS(投資回収_月次!$S$8:$S$127,投資回収_月次!$C$8:$C$127,B7)</f>
@@ -21665,7 +21741,7 @@
       </c>
       <c r="I7" s="39" t="n">
         <f aca="false">E7-F7-G7-H7</f>
-        <v>1517140</v>
+        <v>1467140</v>
       </c>
       <c r="J7" s="39" t="n">
         <f aca="false">SUM(E$5:E7)</f>
@@ -21673,15 +21749,15 @@
       </c>
       <c r="K7" s="39" t="n">
         <f aca="false">MAX(前提条件!$C$94-J7,0)</f>
-        <v>0</v>
+        <v>252184</v>
       </c>
       <c r="L7" s="39" t="n">
         <f aca="false">前提条件!$C$8-SUM(F$5:F7)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(G$5:G7),0)</f>
-        <v>3412500</v>
+        <v>3791666.66666667</v>
       </c>
       <c r="M7" s="39" t="n">
         <f aca="false">SUM(I$5:I7)</f>
-        <v>3660316</v>
+        <v>3539482.66666667</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21706,7 +21782,7 @@
       </c>
       <c r="G8" s="29" t="n">
         <f aca="false">SUMIFS(投資回収_月次!$R$8:$R$127,投資回収_月次!$C$8:$C$127,B8)</f>
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="H8" s="29" t="n">
         <f aca="false">SUMIFS(投資回収_月次!$S$8:$S$127,投資回収_月次!$C$8:$C$127,B8)</f>
@@ -21714,7 +21790,7 @@
       </c>
       <c r="I8" s="39" t="n">
         <f aca="false">E8-F8-G8-H8</f>
-        <v>1517140</v>
+        <v>1467140</v>
       </c>
       <c r="J8" s="39" t="n">
         <f aca="false">SUM(E$5:E8)</f>
@@ -21726,11 +21802,11 @@
       </c>
       <c r="L8" s="39" t="n">
         <f aca="false">前提条件!$C$8-SUM(F$5:F8)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(G$5:G8),0)</f>
-        <v>2962500</v>
+        <v>3291666.66666667</v>
       </c>
       <c r="M8" s="39" t="n">
         <f aca="false">SUM(I$5:I8)</f>
-        <v>5177456</v>
+        <v>5006622.66666667</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21755,7 +21831,7 @@
       </c>
       <c r="G9" s="29" t="n">
         <f aca="false">SUMIFS(投資回収_月次!$R$8:$R$127,投資回収_月次!$C$8:$C$127,B9)</f>
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="H9" s="29" t="n">
         <f aca="false">SUMIFS(投資回収_月次!$S$8:$S$127,投資回収_月次!$C$8:$C$127,B9)</f>
@@ -21763,7 +21839,7 @@
       </c>
       <c r="I9" s="39" t="n">
         <f aca="false">E9-F9-G9-H9</f>
-        <v>1517140</v>
+        <v>1467140</v>
       </c>
       <c r="J9" s="39" t="n">
         <f aca="false">SUM(E$5:E9)</f>
@@ -21775,11 +21851,11 @@
       </c>
       <c r="L9" s="39" t="n">
         <f aca="false">前提条件!$C$8-SUM(F$5:F9)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(G$5:G9),0)</f>
-        <v>2512500</v>
+        <v>2791666.66666667</v>
       </c>
       <c r="M9" s="39" t="n">
         <f aca="false">SUM(I$5:I9)</f>
-        <v>6694596</v>
+        <v>6473762.66666667</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21804,7 +21880,7 @@
       </c>
       <c r="G10" s="29" t="n">
         <f aca="false">SUMIFS(投資回収_月次!$R$8:$R$127,投資回収_月次!$C$8:$C$127,B10)</f>
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="H10" s="29" t="n">
         <f aca="false">SUMIFS(投資回収_月次!$S$8:$S$127,投資回収_月次!$C$8:$C$127,B10)</f>
@@ -21812,7 +21888,7 @@
       </c>
       <c r="I10" s="39" t="n">
         <f aca="false">E10-F10-G10-H10</f>
-        <v>1522776</v>
+        <v>1472776</v>
       </c>
       <c r="J10" s="39" t="n">
         <f aca="false">SUM(E$5:E10)</f>
@@ -21824,11 +21900,11 @@
       </c>
       <c r="L10" s="39" t="n">
         <f aca="false">前提条件!$C$8-SUM(F$5:F10)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(G$5:G10),0)</f>
-        <v>2062500</v>
+        <v>2291666.66666667</v>
       </c>
       <c r="M10" s="39" t="n">
         <f aca="false">SUM(I$5:I10)</f>
-        <v>8217372</v>
+        <v>7946538.66666667</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21853,7 +21929,7 @@
       </c>
       <c r="G11" s="29" t="n">
         <f aca="false">SUMIFS(投資回収_月次!$R$8:$R$127,投資回収_月次!$C$8:$C$127,B11)</f>
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="H11" s="29" t="n">
         <f aca="false">SUMIFS(投資回収_月次!$S$8:$S$127,投資回収_月次!$C$8:$C$127,B11)</f>
@@ -21861,7 +21937,7 @@
       </c>
       <c r="I11" s="39" t="n">
         <f aca="false">E11-F11-G11-H11</f>
-        <v>1517140</v>
+        <v>1467140</v>
       </c>
       <c r="J11" s="39" t="n">
         <f aca="false">SUM(E$5:E11)</f>
@@ -21873,11 +21949,11 @@
       </c>
       <c r="L11" s="39" t="n">
         <f aca="false">前提条件!$C$8-SUM(F$5:F11)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(G$5:G11),0)</f>
-        <v>1612500</v>
+        <v>1791666.66666667</v>
       </c>
       <c r="M11" s="39" t="n">
         <f aca="false">SUM(I$5:I11)</f>
-        <v>9734512</v>
+        <v>9413678.66666667</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21902,7 +21978,7 @@
       </c>
       <c r="G12" s="29" t="n">
         <f aca="false">SUMIFS(投資回収_月次!$R$8:$R$127,投資回収_月次!$C$8:$C$127,B12)</f>
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="H12" s="29" t="n">
         <f aca="false">SUMIFS(投資回収_月次!$S$8:$S$127,投資回収_月次!$C$8:$C$127,B12)</f>
@@ -21910,7 +21986,7 @@
       </c>
       <c r="I12" s="39" t="n">
         <f aca="false">E12-F12-G12-H12</f>
-        <v>1517140</v>
+        <v>1467140</v>
       </c>
       <c r="J12" s="39" t="n">
         <f aca="false">SUM(E$5:E12)</f>
@@ -21922,11 +21998,11 @@
       </c>
       <c r="L12" s="39" t="n">
         <f aca="false">前提条件!$C$8-SUM(F$5:F12)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(G$5:G12),0)</f>
-        <v>1162500</v>
+        <v>1291666.66666667</v>
       </c>
       <c r="M12" s="39" t="n">
         <f aca="false">SUM(I$5:I12)</f>
-        <v>11251652</v>
+        <v>10880818.6666667</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21951,7 +22027,7 @@
       </c>
       <c r="G13" s="29" t="n">
         <f aca="false">SUMIFS(投資回収_月次!$R$8:$R$127,投資回収_月次!$C$8:$C$127,B13)</f>
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="H13" s="29" t="n">
         <f aca="false">SUMIFS(投資回収_月次!$S$8:$S$127,投資回収_月次!$C$8:$C$127,B13)</f>
@@ -21959,7 +22035,7 @@
       </c>
       <c r="I13" s="39" t="n">
         <f aca="false">E13-F13-G13-H13</f>
-        <v>1517140</v>
+        <v>1467140</v>
       </c>
       <c r="J13" s="39" t="n">
         <f aca="false">SUM(E$5:E13)</f>
@@ -21971,11 +22047,11 @@
       </c>
       <c r="L13" s="39" t="n">
         <f aca="false">前提条件!$C$8-SUM(F$5:F13)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(G$5:G13),0)</f>
-        <v>712500</v>
+        <v>791666.666666667</v>
       </c>
       <c r="M13" s="39" t="n">
         <f aca="false">SUM(I$5:I13)</f>
-        <v>12768792</v>
+        <v>12347958.6666667</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22000,7 +22076,7 @@
       </c>
       <c r="G14" s="29" t="n">
         <f aca="false">SUMIFS(投資回収_月次!$R$8:$R$127,投資回収_月次!$C$8:$C$127,B14)</f>
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="H14" s="29" t="n">
         <f aca="false">SUMIFS(投資回収_月次!$S$8:$S$127,投資回収_月次!$C$8:$C$127,B14)</f>
@@ -22008,7 +22084,7 @@
       </c>
       <c r="I14" s="39" t="n">
         <f aca="false">E14-F14-G14-H14</f>
-        <v>1522776</v>
+        <v>1472776</v>
       </c>
       <c r="J14" s="39" t="n">
         <f aca="false">SUM(E$5:E14)</f>
@@ -22020,11 +22096,11 @@
       </c>
       <c r="L14" s="39" t="n">
         <f aca="false">前提条件!$C$8-SUM(F$5:F14)+IF(前提条件!$C$86&lt;3,前提条件!$C$85-SUM(G$5:G14),0)</f>
-        <v>262500</v>
+        <v>291666.666666667</v>
       </c>
       <c r="M14" s="39" t="n">
         <f aca="false">SUM(I$5:I14)</f>
-        <v>14291568</v>
+        <v>13820734.6666667</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22049,7 +22125,7 @@
       </c>
       <c r="G15" s="29" t="n">
         <f aca="false">SUMIFS(投資回収_月次!$R$8:$R$127,投資回収_月次!$C$8:$C$127,B15)</f>
-        <v>0</v>
+        <v>29166.6666666667</v>
       </c>
       <c r="H15" s="29" t="n">
         <f aca="false">SUMIFS(投資回収_月次!$S$8:$S$127,投資回収_月次!$C$8:$C$127,B15)</f>
@@ -22057,7 +22133,7 @@
       </c>
       <c r="I15" s="39" t="n">
         <f aca="false">E15-F15-G15-H15</f>
-        <v>896740</v>
+        <v>867573.333333333</v>
       </c>
       <c r="J15" s="39" t="n">
         <f aca="false">SUM(E$5:E15)</f>
@@ -22073,7 +22149,7 @@
       </c>
       <c r="M15" s="39" t="n">
         <f aca="false">SUM(I$5:I15)</f>
-        <v>15188308</v>
+        <v>14688308</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22095,7 +22171,7 @@
       </c>
       <c r="G16" s="78" t="n">
         <f aca="false">SUM(G5:G15)</f>
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="H16" s="78" t="n">
         <f aca="false">SUM(H5:H15)</f>
@@ -22103,7 +22179,7 @@
       </c>
       <c r="I16" s="78" t="n">
         <f aca="false">SUM(I5:I15)</f>
-        <v>15188308</v>
+        <v>14688308</v>
       </c>
       <c r="J16" s="76"/>
       <c r="K16" s="76"/>
@@ -29945,31 +30021,31 @@
       </c>
       <c r="J79" s="34" t="n">
         <f aca="false">SUMIFS(投資回収_月次!$R$8:$R$127,投資回収_月次!$B$8:$B$127,J$5)/1000</f>
-        <v>0</v>
+        <v>4.16666666666667</v>
       </c>
       <c r="K79" s="34" t="n">
         <f aca="false">SUMIFS(投資回収_月次!$R$8:$R$127,投資回収_月次!$B$8:$B$127,K$5)/1000</f>
-        <v>0</v>
+        <v>4.16666666666667</v>
       </c>
       <c r="L79" s="34" t="n">
         <f aca="false">SUMIFS(投資回収_月次!$R$8:$R$127,投資回収_月次!$B$8:$B$127,L$5)/1000</f>
-        <v>0</v>
+        <v>4.16666666666667</v>
       </c>
       <c r="M79" s="34" t="n">
         <f aca="false">SUMIFS(投資回収_月次!$R$8:$R$127,投資回収_月次!$B$8:$B$127,M$5)/1000</f>
-        <v>0</v>
+        <v>4.16666666666667</v>
       </c>
       <c r="N79" s="34" t="n">
         <f aca="false">SUMIFS(投資回収_月次!$R$8:$R$127,投資回収_月次!$B$8:$B$127,N$5)/1000</f>
-        <v>0</v>
+        <v>4.16666666666667</v>
       </c>
       <c r="O79" s="72" t="n">
         <f aca="false">SUM(C79:N79)</f>
-        <v>0</v>
+        <v>20.8333333333333</v>
       </c>
       <c r="P79" s="72" t="n">
         <f aca="false">SUM(I79:N79)</f>
-        <v>0</v>
+        <v>20.8333333333333</v>
       </c>
       <c r="Q79" s="14" t="s">
         <v>368</v>
@@ -30073,31 +30149,31 @@
       </c>
       <c r="J81" s="91" t="n">
         <f aca="false">SUM(J74:J80)</f>
-        <v>-112.808</v>
+        <v>-108.641333333333</v>
       </c>
       <c r="K81" s="91" t="n">
         <f aca="false">SUM(K74:K80)</f>
-        <v>-129.716</v>
+        <v>-125.549333333333</v>
       </c>
       <c r="L81" s="91" t="n">
         <f aca="false">SUM(L74:L80)</f>
-        <v>-124.08</v>
+        <v>-119.913333333333</v>
       </c>
       <c r="M81" s="91" t="n">
         <f aca="false">SUM(M74:M80)</f>
-        <v>-129.716</v>
+        <v>-125.549333333333</v>
       </c>
       <c r="N81" s="91" t="n">
         <f aca="false">SUM(N74:N80)</f>
-        <v>-124.08</v>
+        <v>-119.913333333333</v>
       </c>
       <c r="O81" s="91" t="n">
         <f aca="false">SUM(O74:O80)</f>
-        <v>-620.4</v>
+        <v>-599.566666666667</v>
       </c>
       <c r="P81" s="91" t="n">
         <f aca="false">SUM(P74:P80)</f>
-        <v>-620.4</v>
+        <v>-599.566666666667</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30134,31 +30210,31 @@
       </c>
       <c r="J82" s="93" t="n">
         <f aca="false">-J81</f>
-        <v>112.808</v>
+        <v>108.641333333333</v>
       </c>
       <c r="K82" s="93" t="n">
         <f aca="false">-K81</f>
-        <v>129.716</v>
+        <v>125.549333333333</v>
       </c>
       <c r="L82" s="93" t="n">
         <f aca="false">-L81</f>
-        <v>124.08</v>
+        <v>119.913333333333</v>
       </c>
       <c r="M82" s="93" t="n">
         <f aca="false">-M81</f>
-        <v>129.716</v>
+        <v>125.549333333333</v>
       </c>
       <c r="N82" s="93" t="n">
         <f aca="false">-N81</f>
-        <v>124.08</v>
+        <v>119.913333333333</v>
       </c>
       <c r="O82" s="93" t="n">
         <f aca="false">-O81</f>
-        <v>620.4</v>
+        <v>599.566666666667</v>
       </c>
       <c r="P82" s="93" t="n">
         <f aca="false">-P81</f>
-        <v>620.4</v>
+        <v>599.566666666667</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30256,31 +30332,31 @@
       </c>
       <c r="J84" s="95" t="n">
         <f aca="false">IF((J78+J79)=0,"-",J83/(J78+J79))</f>
-        <v>4.00821333333333</v>
+        <v>3.607392</v>
       </c>
       <c r="K84" s="95" t="n">
         <f aca="false">IF((K78+K79)=0,"-",K83/(K78+K79))</f>
-        <v>4.45909333333333</v>
+        <v>4.013184</v>
       </c>
       <c r="L84" s="95" t="n">
         <f aca="false">IF((L78+L79)=0,"-",L83/(L78+L79))</f>
-        <v>4.3088</v>
+        <v>3.87792</v>
       </c>
       <c r="M84" s="95" t="n">
         <f aca="false">IF((M78+M79)=0,"-",M83/(M78+M79))</f>
-        <v>4.45909333333333</v>
+        <v>4.013184</v>
       </c>
       <c r="N84" s="95" t="n">
         <f aca="false">IF((N78+N79)=0,"-",N83/(N78+N79))</f>
-        <v>4.3088</v>
+        <v>3.87792</v>
       </c>
       <c r="O84" s="95" t="n">
         <f aca="false">IF((O78+O79)=0,"-",O83/(O78+O79))</f>
-        <v>4.3088</v>
+        <v>3.87792</v>
       </c>
       <c r="P84" s="95" t="n">
         <f aca="false">IF((P78+P79)=0,"-",P83/(P78+P79))</f>
-        <v>4.3088</v>
+        <v>3.87792</v>
       </c>
       <c r="Q84" s="14" t="s">
         <v>375</v>
@@ -32297,31 +32373,31 @@
       </c>
       <c r="J119" s="96" t="n">
         <f aca="false">SUM(J120:J140)</f>
-        <v>72654.4737</v>
+        <v>72658.6403666667</v>
       </c>
       <c r="K119" s="96" t="n">
         <f aca="false">SUM(K120:K140)</f>
-        <v>85345.3957</v>
+        <v>85349.5623666667</v>
       </c>
       <c r="L119" s="96" t="n">
         <f aca="false">SUM(L120:L140)</f>
-        <v>79672.3817</v>
+        <v>79676.5483666667</v>
       </c>
       <c r="M119" s="96" t="n">
         <f aca="false">SUM(M120:M140)</f>
-        <v>78818.4957</v>
+        <v>78822.6623666667</v>
       </c>
       <c r="N119" s="96" t="n">
         <f aca="false">SUM(N120:N140)</f>
-        <v>78340.3817</v>
+        <v>78344.5483666667</v>
       </c>
       <c r="O119" s="72" t="n">
         <f aca="false">SUM(C119:N119)</f>
-        <v>941201.6848</v>
+        <v>941222.518133333</v>
       </c>
       <c r="P119" s="72" t="n">
         <f aca="false">SUM(I119:N119)</f>
-        <v>469165.2876</v>
+        <v>469186.120933333</v>
       </c>
       <c r="Q119" s="14" t="s">
         <v>377</v>
@@ -33468,31 +33544,31 @@
       </c>
       <c r="J138" s="98" t="n">
         <f aca="false">J59+J78+J79</f>
-        <v>12514.0617</v>
+        <v>12518.2283666667</v>
       </c>
       <c r="K138" s="98" t="n">
         <f aca="false">K59+K78+K79</f>
-        <v>12514.0617</v>
+        <v>12518.2283666667</v>
       </c>
       <c r="L138" s="98" t="n">
         <f aca="false">L59+L78+L79</f>
-        <v>12514.0617</v>
+        <v>12518.2283666667</v>
       </c>
       <c r="M138" s="98" t="n">
         <f aca="false">M59+M78+M79</f>
-        <v>12514.0617</v>
+        <v>12518.2283666667</v>
       </c>
       <c r="N138" s="98" t="n">
         <f aca="false">N59+N78+N79</f>
-        <v>12514.0617</v>
+        <v>12518.2283666667</v>
       </c>
       <c r="O138" s="98" t="n">
         <f aca="false">SUM(C138:N138)</f>
-        <v>141476.8235</v>
+        <v>141497.656833333</v>
       </c>
       <c r="P138" s="98" t="n">
         <f aca="false">SUM(I138:N138)</f>
-        <v>74796.8702</v>
+        <v>74817.7035333333</v>
       </c>
       <c r="Q138" s="45" t="s">
         <v>378</v>
@@ -33654,31 +33730,31 @@
       </c>
       <c r="J141" s="96" t="n">
         <f aca="false">J102+J112+J115+J119</f>
-        <v>209564.0737</v>
+        <v>209568.240366667</v>
       </c>
       <c r="K141" s="96" t="n">
         <f aca="false">K102+K112+K115+K119</f>
-        <v>230924.7457</v>
+        <v>230928.912366667</v>
       </c>
       <c r="L141" s="96" t="n">
         <f aca="false">L102+L112+L115+L119</f>
-        <v>220915.4817</v>
+        <v>220919.648366667</v>
       </c>
       <c r="M141" s="96" t="n">
         <f aca="false">M102+M112+M115+M119</f>
-        <v>225059.8457</v>
+        <v>225064.012366667</v>
       </c>
       <c r="N141" s="96" t="n">
         <f aca="false">N102+N112+N115+N119</f>
-        <v>222845.4817</v>
+        <v>222849.648366667</v>
       </c>
       <c r="O141" s="72" t="n">
         <f aca="false">SUM(C141:N141)</f>
-        <v>2651675.3848</v>
+        <v>2651696.21813333</v>
       </c>
       <c r="P141" s="72" t="n">
         <f aca="false">SUM(I141:N141)</f>
-        <v>1330425.3876</v>
+        <v>1330446.22093333</v>
       </c>
       <c r="Q141" s="14" t="s">
         <v>377</v>
@@ -33779,31 +33855,31 @@
       </c>
       <c r="J143" s="96" t="n">
         <f aca="false">J88-J141+J142</f>
-        <v>-2452.67370000001</v>
+        <v>-2456.84036666667</v>
       </c>
       <c r="K143" s="96" t="n">
         <f aca="false">K88-K141+K142</f>
-        <v>3584.25429999997</v>
+        <v>3580.08763333334</v>
       </c>
       <c r="L143" s="96" t="n">
         <f aca="false">L88-L141+L142</f>
-        <v>3864.5183</v>
+        <v>3860.35163333331</v>
       </c>
       <c r="M143" s="96" t="n">
         <f aca="false">M88-M141+M142</f>
-        <v>2540.15429999999</v>
+        <v>2535.98763333331</v>
       </c>
       <c r="N143" s="96" t="n">
         <f aca="false">N88-N141+N142</f>
-        <v>-3598.21309999999</v>
+        <v>-3602.37976666668</v>
       </c>
       <c r="O143" s="72" t="n">
         <f aca="false">SUM(C143:N143)</f>
-        <v>28611.2717999999</v>
+        <v>28590.4384666665</v>
       </c>
       <c r="P143" s="72" t="n">
         <f aca="false">SUM(I143:N143)</f>
-        <v>1618.14399999994</v>
+        <v>1597.3106666666</v>
       </c>
       <c r="Q143" s="14" t="s">
         <v>377</v>
@@ -34148,31 +34224,31 @@
       </c>
       <c r="J149" s="93" t="n">
         <f aca="false">J143+J144-J145-J146-J147-J148</f>
-        <v>-2452.67370000001</v>
+        <v>-2456.84036666667</v>
       </c>
       <c r="K149" s="93" t="n">
         <f aca="false">K143+K144-K145-K146-K147-K148</f>
-        <v>3584.25429999997</v>
+        <v>3580.08763333334</v>
       </c>
       <c r="L149" s="93" t="n">
         <f aca="false">L143+L144-L145-L146-L147-L148</f>
-        <v>3864.5183</v>
+        <v>3860.35163333331</v>
       </c>
       <c r="M149" s="93" t="n">
         <f aca="false">M143+M144-M145-M146-M147-M148</f>
-        <v>2540.15429999999</v>
+        <v>2535.98763333331</v>
       </c>
       <c r="N149" s="93" t="n">
         <f aca="false">N143+N144-N145-N146-N147-N148</f>
-        <v>-3598.21309999999</v>
+        <v>-3602.37976666668</v>
       </c>
       <c r="O149" s="99" t="n">
         <f aca="false">SUM(C149:N149)</f>
-        <v>28611.2717999999</v>
+        <v>28590.4384666665</v>
       </c>
       <c r="P149" s="99" t="n">
         <f aca="false">SUM(I149:N149)</f>
-        <v>1618.14399999994</v>
+        <v>1597.3106666666</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34292,31 +34368,31 @@
       </c>
       <c r="J153" s="96" t="n">
         <f aca="false">J149</f>
-        <v>-2452.67370000001</v>
+        <v>-2456.84036666667</v>
       </c>
       <c r="K153" s="96" t="n">
         <f aca="false">K149</f>
-        <v>3584.25429999997</v>
+        <v>3580.08763333334</v>
       </c>
       <c r="L153" s="96" t="n">
         <f aca="false">L149</f>
-        <v>3864.5183</v>
+        <v>3860.35163333331</v>
       </c>
       <c r="M153" s="96" t="n">
         <f aca="false">M149</f>
-        <v>2540.15429999999</v>
+        <v>2535.98763333331</v>
       </c>
       <c r="N153" s="96" t="n">
         <f aca="false">N149</f>
-        <v>-3598.21309999999</v>
+        <v>-3602.37976666668</v>
       </c>
       <c r="O153" s="96" t="n">
         <f aca="false">O149</f>
-        <v>28611.2717999999</v>
+        <v>28590.4384666665</v>
       </c>
       <c r="P153" s="96" t="n">
         <f aca="false">P149</f>
-        <v>1618.14399999994</v>
+        <v>1597.3106666666</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34353,31 +34429,31 @@
       </c>
       <c r="J154" s="93" t="n">
         <f aca="false">J153-J152</f>
-        <v>112.808000000019</v>
+        <v>108.641333333362</v>
       </c>
       <c r="K154" s="93" t="n">
         <f aca="false">K153-K152</f>
-        <v>129.715999999985</v>
+        <v>125.549333333357</v>
       </c>
       <c r="L154" s="93" t="n">
         <f aca="false">L153-L152</f>
-        <v>124.080000000016</v>
+        <v>119.91333333333</v>
       </c>
       <c r="M154" s="93" t="n">
         <f aca="false">M153-M152</f>
-        <v>129.716000000015</v>
+        <v>125.549333333329</v>
       </c>
       <c r="N154" s="93" t="n">
         <f aca="false">N153-N152</f>
-        <v>124.080000000016</v>
+        <v>119.91333333333</v>
       </c>
       <c r="O154" s="93" t="n">
         <f aca="false">O153-O152</f>
-        <v>620.400000000052</v>
+        <v>599.566666666709</v>
       </c>
       <c r="P154" s="93" t="n">
         <f aca="false">P153-P152</f>
-        <v>620.400000000052</v>
+        <v>599.566666666709</v>
       </c>
       <c r="Q154" s="14" t="s">
         <v>384</v>
@@ -34539,31 +34615,31 @@
       </c>
       <c r="J157" s="101" t="n">
         <f aca="false">IF(J8=0,0,J149/J8)</f>
-        <v>-0.00336166899671055</v>
+        <v>-0.0033673798885234</v>
       </c>
       <c r="K157" s="101" t="n">
         <f aca="false">IF(K8=0,0,K149/K8)</f>
-        <v>0.00433666581972168</v>
+        <v>0.0043316244807421</v>
       </c>
       <c r="L157" s="101" t="n">
         <f aca="false">IF(L8=0,0,L149/L8)</f>
-        <v>0.00487944229797979</v>
+        <v>0.00487418135521883</v>
       </c>
       <c r="M157" s="101" t="n">
         <f aca="false">IF(M8=0,0,M149/M8)</f>
-        <v>0.0031672746882793</v>
+        <v>0.00316207934330836</v>
       </c>
       <c r="N157" s="101" t="n">
         <f aca="false">IF(N8=0,0,N149/N8)</f>
-        <v>-0.00463090489060488</v>
+        <v>-0.00463626739596741</v>
       </c>
       <c r="O157" s="101" t="n">
         <f aca="false">IF(O8=0,0,O149/O8)</f>
-        <v>0.00303099987471561</v>
+        <v>0.00302879284836723</v>
       </c>
       <c r="P157" s="101" t="n">
         <f aca="false">IF(P8=0,0,P149/P8)</f>
-        <v>0.000344482395747795</v>
+        <v>0.00034004724252405</v>
       </c>
     </row>
   </sheetData>

--- a/充填機投資回収_白鳥惣菜_48期.xlsx
+++ b/充填機投資回収_白鳥惣菜_48期.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="387">
   <si>
     <t xml:space="preserve">充填機導入　投資回収計画（白鳥惣菜）</t>
   </si>
@@ -223,7 +223,7 @@
     <t xml:space="preserve">台数</t>
   </si>
   <si>
-    <t xml:space="preserve">投資額（取得価額）</t>
+    <t xml:space="preserve">充填機本体（取得価額）</t>
   </si>
   <si>
     <t xml:space="preserve">対象商品</t>
@@ -238,13 +238,13 @@
     <t xml:space="preserve">減価償却（機械）</t>
   </si>
   <si>
-    <t xml:space="preserve">電気工事費</t>
-  </si>
-  <si>
-    <t xml:space="preserve">電気工事の会計処理</t>
-  </si>
-  <si>
-    <t xml:space="preserve">総投資額（機械＋電気工事）</t>
+    <t xml:space="preserve">電気・付帯工事費</t>
+  </si>
+  <si>
+    <t xml:space="preserve">電気・付帯工事の会計処理</t>
+  </si>
+  <si>
+    <t xml:space="preserve">総投資額（機械＋電気・付帯工事）</t>
   </si>
   <si>
     <t xml:space="preserve">■ 結論（月平均）</t>
@@ -285,7 +285,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">か月）＋電気工事（資産計上時）</t>
+      <t xml:space="preserve">か月）＋電気・付帯工事（資産計上時）</t>
     </r>
   </si>
   <si>
@@ -1233,7 +1233,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">・電気工事費</t>
+      <t xml:space="preserve">・電気・付帯工事費</t>
     </r>
     <r>
       <rPr>
@@ -1302,7 +1302,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">■ 電気工事費が発生した場合の</t>
+      <t xml:space="preserve">■ 電気・付帯工事費が発生した場合の</t>
     </r>
     <r>
       <rPr>
@@ -1334,7 +1334,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">電気工事なしの場合の予算差（円）　</t>
+      <t xml:space="preserve">電気・付帯工事なしの場合の予算差（円）　</t>
     </r>
     <r>
       <rPr>
@@ -1381,7 +1381,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">電気工事費（円）
+    <t xml:space="preserve">電気・付帯工事費（円）
 ※青字は変更可</t>
   </si>
   <si>
@@ -1783,7 +1783,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">・実際の工事費は「前提条件」の電気工事費・処理区分に入力すると、</t>
+      <t xml:space="preserve">・実際の工事費は「前提条件」の電気・付帯工事費・処理区分に入力すると、</t>
     </r>
     <r>
       <rPr>
@@ -1822,7 +1822,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">投資額（充填機</t>
+      <t xml:space="preserve">充填機本体（</t>
     </r>
     <r>
       <rPr>
@@ -1911,13 +1911,13 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">付帯費用（搬入・設置・試運転）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">見積に含まれていなければ入力</t>
-  </si>
-  <si>
-    <t xml:space="preserve">取得価額合計</t>
+    <t xml:space="preserve">電源・配線、搬入・設置・試運転をまとめて下部「■ 電気・付帯工事費」で入力</t>
+  </si>
+  <si>
+    <t xml:space="preserve">機械本体の取得価額（償却対象）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">電気・付帯工事分の償却は下部の処理区分に従い別計算</t>
   </si>
   <si>
     <t xml:space="preserve">耐用年数（減価償却・定額法）</t>
@@ -2174,7 +2174,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">※電気工事費は下部「■ 電気工事費」で入力（総投資額 →）</t>
+    <t xml:space="preserve">総投資額（機械本体＋電気・付帯工事）→</t>
   </si>
   <si>
     <t xml:space="preserve">■ 機械仕様（カタログ値）</t>
@@ -3347,10 +3347,10 @@
     <t xml:space="preserve">月平均 純効果（キャッシュ）</t>
   </si>
   <si>
-    <t xml:space="preserve">年間 減価償却費（機械＋電気工事）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">電気工事を一括費用にした場合は導入月のみ別途計上</t>
+    <t xml:space="preserve">年間 減価償却費（機械＋電気・付帯工事）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">電気・付帯工事を一括費用にした場合は導入月のみ別途計上</t>
   </si>
   <si>
     <t xml:space="preserve">年間 利益改善額（減価償却後）</t>
@@ -3393,7 +3393,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">総投資額（機械＋電気工事）</t>
+      <t xml:space="preserve">総投資額（機械＋電気・付帯工事）</t>
     </r>
     <r>
       <rPr>
@@ -3430,7 +3430,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">■ 電気工事費（</t>
+      <t xml:space="preserve">■ 電気・付帯工事費（</t>
     </r>
     <r>
       <rPr>
@@ -3451,11 +3451,11 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">電源・配線工事など）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">電気工事費（税抜）</t>
+      <t xml:space="preserve">電源・配線、搬入・設置・試運転）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">電気・付帯工事費（税抜）</t>
   </si>
   <si>
     <r>
@@ -3484,7 +3484,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">万円（区分</t>
+      <t xml:space="preserve">万円（電気・付帯工事＋付帯工事の合計・区分</t>
     </r>
     <r>
       <rPr>
@@ -3714,10 +3714,10 @@
     <t xml:space="preserve">適用する償却年数</t>
   </si>
   <si>
-    <t xml:space="preserve">電気工事 月額減価償却費</t>
-  </si>
-  <si>
-    <t xml:space="preserve">電気工事 一括費用計上額（導入月）</t>
+    <t xml:space="preserve">電気・付帯工事 月額減価償却費</t>
+  </si>
+  <si>
+    <t xml:space="preserve">電気・付帯工事 一括費用計上額（導入月）</t>
   </si>
   <si>
     <r>
@@ -4147,11 +4147,11 @@
     <t xml:space="preserve">回収判定</t>
   </si>
   <si>
-    <t xml:space="preserve">電気工事
+    <t xml:space="preserve">電気・付帯工事
 減価償却費</t>
   </si>
   <si>
-    <t xml:space="preserve">電気工事
+    <t xml:space="preserve">電気・付帯工事
 一括費用</t>
   </si>
   <si>
@@ -4328,7 +4328,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">か月分。電気工事費は「前提条件」下部で入力</t>
+      <t xml:space="preserve">か月分。電気・付帯工事費は「前提条件」下部で入力</t>
     </r>
   </si>
   <si>
@@ -4391,7 +4391,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">電気工事</t>
+      <t xml:space="preserve">電気・付帯工事</t>
     </r>
     <r>
       <rPr>
@@ -4436,7 +4436,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">電気工事</t>
+      <t xml:space="preserve">電気・付帯工事</t>
     </r>
     <r>
       <rPr>
@@ -4525,7 +4525,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">＝人件費・絞り袋の削減額から電気・洗浄・保守部品費を差し引いた手残り（減価償却前）。投資回収はこの累計と総投資額（機械＋電気工事）で判定。</t>
+      <t xml:space="preserve">＝人件費・絞り袋の削減額から電気・洗浄・保守部品費を差し引いた手残り（減価償却前）。投資回収はこの累計と総投資額（機械＋電気・付帯工事）で判定。</t>
     </r>
   </si>
   <si>
@@ -4536,7 +4536,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">・利益影響＝純効果 − 減価償却費（機械・電気工事）− 電気工事の一括費用。</t>
+      <t xml:space="preserve">・利益影響＝純効果 − 減価償却費（機械・電気・付帯工事）− 電気・付帯工事の一括費用。</t>
     </r>
     <r>
       <rPr>
@@ -4566,7 +4566,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">・黄色の行＝投資額を回収し終える期。電気工事が</t>
+      <t xml:space="preserve">・黄色の行＝投資額を回収し終える期。電気・付帯工事が</t>
     </r>
     <r>
       <rPr>
@@ -5964,7 +5964,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">減価償却費（電気工事）</t>
+    <t xml:space="preserve">減価償却費（電気・付帯工事）</t>
   </si>
   <si>
     <r>
@@ -5974,7 +5974,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">電気工事を資産計上（区分</t>
+      <t xml:space="preserve">電気・付帯工事を資産計上（区分</t>
     </r>
     <r>
       <rPr>
@@ -6016,7 +6016,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">修繕費（電気工事・一括費用）</t>
+    <t xml:space="preserve">修繕費（電気・付帯工事・一括費用）</t>
   </si>
   <si>
     <r>
@@ -6236,7 +6236,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">電気工事なしなら</t>
+      <t xml:space="preserve">電気・付帯工事なしなら</t>
     </r>
     <r>
       <rPr>
@@ -7447,11 +7447,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="58409866"/>
-        <c:axId val="84522642"/>
+        <c:axId val="61558352"/>
+        <c:axId val="72189669"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="58409866"/>
+        <c:axId val="61558352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7483,7 +7483,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84522642"/>
+        <c:crossAx val="72189669"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7491,7 +7491,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="84522642"/>
+        <c:axId val="72189669"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7533,7 +7533,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58409866"/>
+        <c:crossAx val="61558352"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8501,11 +8501,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="10333832"/>
-        <c:axId val="86980223"/>
+        <c:axId val="16180391"/>
+        <c:axId val="96192475"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="10333832"/>
+        <c:axId val="16180391"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8571,7 +8571,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86980223"/>
+        <c:crossAx val="96192475"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8579,7 +8579,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="86980223"/>
+        <c:axId val="96192475"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8655,7 +8655,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10333832"/>
+        <c:crossAx val="16180391"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9027,7 +9027,7 @@
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>減価償却費
-(電気工事)</c:v>
+(電気・付帯工事)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -9160,7 +9160,7 @@
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>一括費用
-(電気工事)</c:v>
+(電気・付帯工事)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -9285,11 +9285,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="63623514"/>
-        <c:axId val="92126230"/>
+        <c:axId val="37847936"/>
+        <c:axId val="33256320"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="63623514"/>
+        <c:axId val="37847936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9321,7 +9321,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92126230"/>
+        <c:crossAx val="33256320"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9329,7 +9329,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="92126230"/>
+        <c:axId val="33256320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9371,7 +9371,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63623514"/>
+        <c:crossAx val="37847936"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9746,11 +9746,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="74049959"/>
-        <c:axId val="1273087"/>
+        <c:axId val="41536326"/>
+        <c:axId val="1078150"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="74049959"/>
+        <c:axId val="41536326"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9782,7 +9782,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1273087"/>
+        <c:crossAx val="1078150"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9790,7 +9790,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1273087"/>
+        <c:axId val="1078150"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9832,7 +9832,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74049959"/>
+        <c:crossAx val="41536326"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11057,30 +11057,33 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" s="38" t="n">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="C7" s="29" t="n">
+        <f aca="false">C85</f>
+        <v>500000</v>
       </c>
       <c r="D7" s="42" t="s">
         <v>82</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C8" s="39" t="n">
-        <f aca="false">C5+C7</f>
+        <f aca="false">C5</f>
         <v>4500000</v>
       </c>
       <c r="D8" s="42" t="s">
         <v>82</v>
       </c>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
